--- a/spider_telephone/最终数据.xlsx
+++ b/spider_telephone/最终数据.xlsx
@@ -432,5769 +432,4327 @@
       <c r="A2" t="n">
         <v>13071302896</v>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>13192099996</v>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>13215124663</v>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>13215132859</v>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>13266012612</v>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>13266252339</v>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>13310807198</v>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>13316627678</v>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>13332627463</v>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>13380159738</v>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>13380168728</v>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>13412001694</v>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13412121698</v>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>13412209436</v>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>13412209597</v>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>13412223422</v>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>13412292787</v>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>13412360278</v>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>13412413200</v>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>13412440837</v>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>13412466407</v>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>13412474974</v>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>13412611516</v>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>13412656245</v>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>13412727974</v>
       </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>13412801160</v>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>13412846148</v>
       </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>13412882445</v>
       </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>13412909682</v>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>13412919173</v>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>13412955840</v>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>13414242486</v>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>13415901819</v>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>13415946829</v>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>13415980602</v>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>13415989968</v>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>13416651139</v>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>13416675918</v>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>13416885775</v>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>13416913243</v>
       </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>13416933639</v>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>13416950113</v>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>13416969354</v>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>13418391419</v>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>13418393842</v>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>13421994713</v>
       </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>13423004212</v>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>13423040355</v>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>13423130366</v>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>13423312331</v>
       </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>13423494869</v>
       </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>13424745879</v>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>13428444253</v>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>13428547393</v>
       </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>13431178860</v>
       </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>13431423431</v>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>13431467571</v>
       </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>13431544143</v>
       </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>13433079049</v>
       </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>13433622189</v>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>13433668649</v>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>13434025637</v>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>13434037309</v>
       </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>13434067130</v>
       </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>13434540706</v>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>13434566550</v>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>13437372214</v>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>13437403045</v>
       </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>13437405014</v>
       </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>13437413376</v>
       </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>13437416490</v>
       </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>13437428489</v>
       </c>
-      <c r="B73" t="n">
-        <v>0</v>
-      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>13450041008</v>
       </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>13450041573</v>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>13450094241</v>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>13450699707</v>
       </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>13480030686</v>
       </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>13480071985</v>
       </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>13480090229</v>
       </c>
-      <c r="B80" t="n">
-        <v>0</v>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>13480450153</v>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
         <v>13500098229</v>
       </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
         <v>13509022281</v>
       </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
         <v>13509022502</v>
       </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
         <v>13509817757</v>
       </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
         <v>13527916519</v>
       </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
         <v>13527936712</v>
       </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>13527942547</v>
       </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
         <v>13527954868</v>
       </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
         <v>13527993664</v>
       </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>13528528636</v>
       </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>13528573727</v>
       </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
         <v>13528605899</v>
       </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
         <v>13528680763</v>
       </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
         <v>13528681975</v>
       </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
         <v>13528697335</v>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
         <v>13532340259</v>
       </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>13532354251</v>
       </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>13532445690</v>
       </c>
-      <c r="B99" t="n">
-        <v>1</v>
-      </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>13532448020</v>
       </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
+      <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
         <v>13532516038</v>
       </c>
-      <c r="B101" t="n">
-        <v>1</v>
-      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
         <v>13532524813</v>
       </c>
-      <c r="B102" t="n">
-        <v>1</v>
-      </c>
+      <c r="B102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>13532535484</v>
       </c>
-      <c r="B103" t="n">
-        <v>1</v>
-      </c>
+      <c r="B103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
         <v>13532551077</v>
       </c>
-      <c r="B104" t="n">
-        <v>1</v>
-      </c>
+      <c r="B104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
         <v>13532580390</v>
       </c>
-      <c r="B105" t="n">
-        <v>1</v>
-      </c>
+      <c r="B105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
         <v>13532637003</v>
       </c>
-      <c r="B106" t="n">
-        <v>1</v>
-      </c>
+      <c r="B106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>13532671042</v>
       </c>
-      <c r="B107" t="n">
-        <v>0</v>
-      </c>
+      <c r="B107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
         <v>13532721023</v>
       </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
+      <c r="B108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
         <v>13532734521</v>
       </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
+      <c r="B109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
         <v>13532739374</v>
       </c>
-      <c r="B110" t="n">
-        <v>1</v>
-      </c>
+      <c r="B110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
         <v>13532811110</v>
       </c>
-      <c r="B111" t="n">
-        <v>1</v>
-      </c>
+      <c r="B111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
         <v>13532811552</v>
       </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
+      <c r="B112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
         <v>13532823367</v>
       </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
+      <c r="B113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
         <v>13532867526</v>
       </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
         <v>13532880082</v>
       </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
+      <c r="B115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
         <v>13532923878</v>
       </c>
-      <c r="B116" t="n">
-        <v>1</v>
-      </c>
+      <c r="B116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
         <v>13532960717</v>
       </c>
-      <c r="B117" t="n">
-        <v>0</v>
-      </c>
+      <c r="B117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
         <v>13532987368</v>
       </c>
-      <c r="B118" t="n">
-        <v>1</v>
-      </c>
+      <c r="B118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
         <v>13532997658</v>
       </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
+      <c r="B119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
         <v>13537043824</v>
       </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
         <v>13537070423</v>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
         <v>13537073529</v>
       </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
+      <c r="B122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
         <v>13537076636</v>
       </c>
-      <c r="B123" t="n">
-        <v>1</v>
-      </c>
+      <c r="B123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
         <v>13537120039</v>
       </c>
-      <c r="B124" t="n">
-        <v>1</v>
-      </c>
+      <c r="B124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
         <v>13537279956</v>
       </c>
-      <c r="B125" t="n">
-        <v>1</v>
-      </c>
+      <c r="B125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
         <v>13537283790</v>
       </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
+      <c r="B126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
         <v>13537408208</v>
       </c>
-      <c r="B127" t="n">
-        <v>1</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
         <v>13537475612</v>
       </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>13537485150</v>
       </c>
-      <c r="B129" t="n">
-        <v>1</v>
-      </c>
+      <c r="B129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>13538359694</v>
       </c>
-      <c r="B130" t="n">
-        <v>1</v>
-      </c>
+      <c r="B130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
         <v>13538429979</v>
       </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
         <v>13538479625</v>
       </c>
-      <c r="B132" t="n">
-        <v>0</v>
-      </c>
+      <c r="B132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
         <v>13538480693</v>
       </c>
-      <c r="B133" t="n">
-        <v>1</v>
-      </c>
+      <c r="B133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
         <v>13538493223</v>
       </c>
-      <c r="B134" t="n">
-        <v>1</v>
-      </c>
+      <c r="B134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
         <v>13538550559</v>
       </c>
-      <c r="B135" t="n">
-        <v>0</v>
-      </c>
+      <c r="B135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
         <v>13538581083</v>
       </c>
-      <c r="B136" t="n">
-        <v>0</v>
-      </c>
+      <c r="B136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
         <v>13538634531</v>
       </c>
-      <c r="B137" t="n">
-        <v>1</v>
-      </c>
+      <c r="B137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
         <v>13538665688</v>
       </c>
-      <c r="B138" t="n">
-        <v>0</v>
-      </c>
+      <c r="B138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
         <v>13538687965</v>
       </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
+      <c r="B139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
         <v>13539002592</v>
       </c>
-      <c r="B140" t="n">
-        <v>0</v>
-      </c>
+      <c r="B140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
         <v>13539002647</v>
       </c>
-      <c r="B141" t="n">
-        <v>0</v>
-      </c>
+      <c r="B141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
         <v>13539024025</v>
       </c>
-      <c r="B142" t="n">
-        <v>0</v>
-      </c>
+      <c r="B142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
         <v>13539038864</v>
       </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
+      <c r="B143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
         <v>13539039426</v>
       </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
+      <c r="B144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
         <v>13539047897</v>
       </c>
-      <c r="B145" t="n">
-        <v>1</v>
-      </c>
+      <c r="B145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
         <v>13539062216</v>
       </c>
-      <c r="B146" t="n">
-        <v>0</v>
-      </c>
+      <c r="B146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>13539086306</v>
       </c>
-      <c r="B147" t="n">
-        <v>0</v>
-      </c>
+      <c r="B147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
         <v>13539089464</v>
       </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
+      <c r="B148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
         <v>13539093337</v>
       </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
+      <c r="B149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
         <v>13543743066</v>
       </c>
-      <c r="B150" t="n">
-        <v>1</v>
-      </c>
+      <c r="B150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
         <v>13543753670</v>
       </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
+      <c r="B151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
         <v>13544654843</v>
       </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
+      <c r="B152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
         <v>13544676043</v>
       </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
+      <c r="B153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
         <v>13544689762</v>
       </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
+      <c r="B154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
         <v>13544709181</v>
       </c>
-      <c r="B155" t="n">
-        <v>0</v>
-      </c>
+      <c r="B155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
         <v>13544710506</v>
       </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
+      <c r="B156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
         <v>13544720070</v>
       </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
+      <c r="B157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
         <v>13544721794</v>
       </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
+      <c r="B158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
         <v>13544766231</v>
       </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
+      <c r="B159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
         <v>13544863168</v>
       </c>
-      <c r="B160" t="n">
-        <v>1</v>
-      </c>
+      <c r="B160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
         <v>13546911933</v>
       </c>
-      <c r="B161" t="n">
-        <v>1</v>
-      </c>
+      <c r="B161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
         <v>13546946294</v>
       </c>
-      <c r="B162" t="n">
-        <v>0</v>
-      </c>
+      <c r="B162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
         <v>13546962609</v>
       </c>
-      <c r="B163" t="n">
-        <v>0</v>
-      </c>
+      <c r="B163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
         <v>13546996722</v>
       </c>
-      <c r="B164" t="n">
-        <v>0</v>
-      </c>
+      <c r="B164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
         <v>13549213072</v>
       </c>
-      <c r="B165" t="n">
-        <v>1</v>
-      </c>
+      <c r="B165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
         <v>13549282116</v>
       </c>
-      <c r="B166" t="n">
-        <v>1</v>
-      </c>
+      <c r="B166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
         <v>13549292803</v>
       </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
+      <c r="B167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
         <v>13549376864</v>
       </c>
-      <c r="B168" t="n">
-        <v>0</v>
-      </c>
+      <c r="B168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
         <v>13553828700</v>
       </c>
-      <c r="B169" t="n">
-        <v>1</v>
-      </c>
+      <c r="B169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
         <v>13553867048</v>
       </c>
-      <c r="B170" t="n">
-        <v>1</v>
-      </c>
+      <c r="B170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
         <v>13556604212</v>
       </c>
-      <c r="B171" t="n">
-        <v>1</v>
-      </c>
+      <c r="B171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
         <v>13556656667</v>
       </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
+      <c r="B172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
         <v>13556685837</v>
       </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
+      <c r="B173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
         <v>13556698476</v>
       </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
+      <c r="B174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
         <v>13556729591</v>
       </c>
-      <c r="B175" t="n">
-        <v>0</v>
-      </c>
+      <c r="B175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
         <v>13556785927</v>
       </c>
-      <c r="B176" t="n">
-        <v>0</v>
-      </c>
+      <c r="B176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
         <v>13559751560</v>
       </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
+      <c r="B177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
         <v>13559782669</v>
       </c>
-      <c r="B178" t="n">
-        <v>0</v>
-      </c>
+      <c r="B178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
         <v>13559794591</v>
       </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
+      <c r="B179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
         <v>13560801360</v>
       </c>
-      <c r="B180" t="n">
-        <v>1</v>
-      </c>
+      <c r="B180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
         <v>13560828081</v>
       </c>
-      <c r="B181" t="n">
-        <v>1</v>
-      </c>
+      <c r="B181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
         <v>13560863234</v>
       </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
+      <c r="B182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
         <v>13560878619</v>
       </c>
-      <c r="B183" t="n">
-        <v>0</v>
-      </c>
+      <c r="B183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
         <v>13580753744</v>
       </c>
-      <c r="B184" t="n">
-        <v>1</v>
-      </c>
+      <c r="B184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
         <v>13580797529</v>
       </c>
-      <c r="B185" t="n">
-        <v>1</v>
-      </c>
+      <c r="B185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
         <v>13580816168</v>
       </c>
-      <c r="B186" t="n">
-        <v>1</v>
-      </c>
+      <c r="B186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
         <v>13580828044</v>
       </c>
-      <c r="B187" t="n">
-        <v>0</v>
-      </c>
+      <c r="B187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
         <v>13580829686</v>
       </c>
-      <c r="B188" t="n">
-        <v>1</v>
-      </c>
+      <c r="B188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
         <v>13580859588</v>
       </c>
-      <c r="B189" t="n">
-        <v>0</v>
-      </c>
+      <c r="B189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
         <v>13580868178</v>
       </c>
-      <c r="B190" t="n">
-        <v>0</v>
-      </c>
+      <c r="B190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
         <v>13580880920</v>
       </c>
-      <c r="B191" t="n">
-        <v>1</v>
-      </c>
+      <c r="B191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
         <v>13580911586</v>
       </c>
-      <c r="B192" t="n">
-        <v>0</v>
-      </c>
+      <c r="B192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
         <v>13580956429</v>
       </c>
-      <c r="B193" t="n">
-        <v>0</v>
-      </c>
+      <c r="B193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
         <v>13580967518</v>
       </c>
-      <c r="B194" t="n">
-        <v>1</v>
-      </c>
+      <c r="B194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
         <v>13592714548</v>
       </c>
-      <c r="B195" t="n">
-        <v>0</v>
-      </c>
+      <c r="B195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
         <v>13592751620</v>
       </c>
-      <c r="B196" t="n">
-        <v>1</v>
-      </c>
+      <c r="B196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
         <v>13592770869</v>
       </c>
-      <c r="B197" t="n">
-        <v>0</v>
-      </c>
+      <c r="B197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
         <v>13600242465</v>
       </c>
-      <c r="B198" t="n">
-        <v>1</v>
-      </c>
+      <c r="B198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
         <v>13600256222</v>
       </c>
-      <c r="B199" t="n">
-        <v>0</v>
-      </c>
+      <c r="B199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
         <v>13600271603</v>
       </c>
-      <c r="B200" t="n">
-        <v>1</v>
-      </c>
+      <c r="B200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
         <v>13602333496</v>
       </c>
-      <c r="B201" t="n">
-        <v>0</v>
-      </c>
+      <c r="B201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
         <v>13602363442</v>
       </c>
-      <c r="B202" t="n">
-        <v>0</v>
-      </c>
+      <c r="B202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
         <v>13602364926</v>
       </c>
-      <c r="B203" t="n">
-        <v>1</v>
-      </c>
+      <c r="B203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
         <v>13602368245</v>
       </c>
-      <c r="B204" t="n">
-        <v>1</v>
-      </c>
+      <c r="B204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
         <v>13602373651</v>
       </c>
-      <c r="B205" t="n">
-        <v>0</v>
-      </c>
+      <c r="B205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
         <v>13602377728</v>
       </c>
-      <c r="B206" t="n">
-        <v>1</v>
-      </c>
+      <c r="B206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
         <v>13602382083</v>
       </c>
-      <c r="B207" t="n">
-        <v>0</v>
-      </c>
+      <c r="B207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
         <v>13602396639</v>
       </c>
-      <c r="B208" t="n">
-        <v>0</v>
-      </c>
+      <c r="B208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
         <v>13602396803</v>
       </c>
-      <c r="B209" t="n">
-        <v>1</v>
-      </c>
+      <c r="B209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
         <v>13609661189</v>
       </c>
-      <c r="B210" t="n">
-        <v>0</v>
-      </c>
+      <c r="B210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
         <v>13612699272</v>
       </c>
-      <c r="B211" t="n">
-        <v>1</v>
-      </c>
+      <c r="B211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
         <v>13612759585</v>
       </c>
-      <c r="B212" t="n">
-        <v>0</v>
-      </c>
+      <c r="B212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
         <v>13620055268</v>
       </c>
-      <c r="B213" t="n">
-        <v>1</v>
-      </c>
+      <c r="B213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
         <v>13622680860</v>
       </c>
-      <c r="B214" t="n">
-        <v>0</v>
-      </c>
+      <c r="B214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
         <v>13622682273</v>
       </c>
-      <c r="B215" t="n">
-        <v>0</v>
-      </c>
+      <c r="B215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
         <v>13622696269</v>
       </c>
-      <c r="B216" t="n">
-        <v>0</v>
-      </c>
+      <c r="B216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
         <v>13631793071</v>
       </c>
-      <c r="B217" t="n">
-        <v>0</v>
-      </c>
+      <c r="B217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
         <v>13642380866</v>
       </c>
-      <c r="B218" t="n">
-        <v>1</v>
-      </c>
+      <c r="B218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
         <v>13642800825</v>
       </c>
-      <c r="B219" t="n">
-        <v>0</v>
-      </c>
+      <c r="B219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
         <v>13642820787</v>
       </c>
-      <c r="B220" t="n">
-        <v>1</v>
-      </c>
+      <c r="B220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
         <v>13642907152</v>
       </c>
-      <c r="B221" t="n">
-        <v>0</v>
-      </c>
+      <c r="B221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
         <v>13642912597</v>
       </c>
-      <c r="B222" t="n">
-        <v>0</v>
-      </c>
+      <c r="B222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
         <v>13642918499</v>
       </c>
-      <c r="B223" t="n">
-        <v>0</v>
-      </c>
+      <c r="B223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
         <v>13642952310</v>
       </c>
-      <c r="B224" t="n">
-        <v>0</v>
-      </c>
+      <c r="B224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
         <v>13649802461</v>
       </c>
-      <c r="B225" t="n">
-        <v>0</v>
-      </c>
+      <c r="B225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
         <v>13649820818</v>
       </c>
-      <c r="B226" t="n">
-        <v>0</v>
-      </c>
+      <c r="B226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
         <v>13650004673</v>
       </c>
-      <c r="B227" t="n">
-        <v>1</v>
-      </c>
+      <c r="B227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
         <v>13650011102</v>
       </c>
-      <c r="B228" t="n">
-        <v>0</v>
-      </c>
+      <c r="B228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
         <v>13650034071</v>
       </c>
-      <c r="B229" t="n">
-        <v>1</v>
-      </c>
+      <c r="B229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
         <v>13650035066</v>
       </c>
-      <c r="B230" t="n">
-        <v>1</v>
-      </c>
+      <c r="B230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
         <v>13650082478</v>
       </c>
-      <c r="B231" t="n">
-        <v>0</v>
-      </c>
+      <c r="B231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
         <v>13650094520</v>
       </c>
-      <c r="B232" t="n">
-        <v>1</v>
-      </c>
+      <c r="B232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
         <v>13650155157</v>
       </c>
-      <c r="B233" t="n">
-        <v>1</v>
-      </c>
+      <c r="B233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
         <v>13650218460</v>
       </c>
-      <c r="B234" t="n">
-        <v>0</v>
-      </c>
+      <c r="B234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
         <v>13650241680</v>
       </c>
-      <c r="B235" t="n">
-        <v>0</v>
-      </c>
+      <c r="B235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
         <v>13650260987</v>
       </c>
-      <c r="B236" t="n">
-        <v>1</v>
-      </c>
+      <c r="B236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
         <v>13650373337</v>
       </c>
-      <c r="B237" t="n">
-        <v>1</v>
-      </c>
+      <c r="B237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
         <v>13650381441</v>
       </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
+      <c r="B238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
         <v>13650382662</v>
       </c>
-      <c r="B239" t="n">
-        <v>1</v>
-      </c>
+      <c r="B239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
         <v>13650399497</v>
       </c>
-      <c r="B240" t="n">
-        <v>0</v>
-      </c>
+      <c r="B240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
         <v>13650429899</v>
       </c>
-      <c r="B241" t="n">
-        <v>0</v>
-      </c>
+      <c r="B241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
         <v>13650448911</v>
       </c>
-      <c r="B242" t="n">
-        <v>0</v>
-      </c>
+      <c r="B242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
         <v>13652488338</v>
       </c>
-      <c r="B243" t="n">
-        <v>1</v>
-      </c>
+      <c r="B243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
         <v>13652490789</v>
       </c>
-      <c r="B244" t="n">
-        <v>1</v>
-      </c>
+      <c r="B244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
         <v>13652510966</v>
       </c>
-      <c r="B245" t="n">
-        <v>0</v>
-      </c>
+      <c r="B245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
         <v>13652521899</v>
       </c>
-      <c r="B246" t="n">
-        <v>1</v>
-      </c>
+      <c r="B246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
         <v>13652525818</v>
       </c>
-      <c r="B247" t="n">
-        <v>0</v>
-      </c>
+      <c r="B247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
         <v>13652530798</v>
       </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
+      <c r="B248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
         <v>13652537477</v>
       </c>
-      <c r="B249" t="n">
-        <v>1</v>
-      </c>
+      <c r="B249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
         <v>13652573083</v>
       </c>
-      <c r="B250" t="n">
-        <v>0</v>
-      </c>
+      <c r="B250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
         <v>13662732748</v>
       </c>
-      <c r="B251" t="n">
-        <v>1</v>
-      </c>
+      <c r="B251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
         <v>13662773663</v>
       </c>
-      <c r="B252" t="n">
-        <v>0</v>
-      </c>
+      <c r="B252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
         <v>13662780007</v>
       </c>
-      <c r="B253" t="n">
-        <v>0</v>
-      </c>
+      <c r="B253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
         <v>13662789728</v>
       </c>
-      <c r="B254" t="n">
-        <v>0</v>
-      </c>
+      <c r="B254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
         <v>13662801795</v>
       </c>
-      <c r="B255" t="n">
-        <v>0</v>
-      </c>
+      <c r="B255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
         <v>13662831504</v>
       </c>
-      <c r="B256" t="n">
-        <v>0</v>
-      </c>
+      <c r="B256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
         <v>13662883917</v>
       </c>
-      <c r="B257" t="n">
-        <v>1</v>
-      </c>
+      <c r="B257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
         <v>13662892550</v>
       </c>
-      <c r="B258" t="n">
-        <v>0</v>
-      </c>
+      <c r="B258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
         <v>13662924782</v>
       </c>
-      <c r="B259" t="n">
-        <v>1</v>
-      </c>
+      <c r="B259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
         <v>13662927220</v>
       </c>
-      <c r="B260" t="n">
-        <v>1</v>
-      </c>
+      <c r="B260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
         <v>13662978731</v>
       </c>
-      <c r="B261" t="n">
-        <v>0</v>
-      </c>
+      <c r="B261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
         <v>13662999728</v>
       </c>
-      <c r="B262" t="n">
-        <v>0</v>
-      </c>
+      <c r="B262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
         <v>13669803831</v>
       </c>
-      <c r="B263" t="n">
-        <v>1</v>
-      </c>
+      <c r="B263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
         <v>13669877757</v>
       </c>
-      <c r="B264" t="n">
-        <v>1</v>
-      </c>
+      <c r="B264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
         <v>13669882415</v>
       </c>
-      <c r="B265" t="n">
-        <v>0</v>
-      </c>
+      <c r="B265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
         <v>13669888939</v>
       </c>
-      <c r="B266" t="n">
-        <v>1</v>
-      </c>
+      <c r="B266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
         <v>13669888944</v>
       </c>
-      <c r="B267" t="n">
-        <v>0</v>
-      </c>
+      <c r="B267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
         <v>13669895661</v>
       </c>
-      <c r="B268" t="n">
-        <v>0</v>
-      </c>
+      <c r="B268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
         <v>13669899465</v>
       </c>
-      <c r="B269" t="n">
-        <v>0</v>
-      </c>
+      <c r="B269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
         <v>13686049100</v>
       </c>
-      <c r="B270" t="n">
-        <v>0</v>
-      </c>
+      <c r="B270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
         <v>13686053379</v>
       </c>
-      <c r="B271" t="n">
-        <v>0</v>
-      </c>
+      <c r="B271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
         <v>13686093776</v>
       </c>
-      <c r="B272" t="n">
-        <v>1</v>
-      </c>
+      <c r="B272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
         <v>13686098107</v>
       </c>
-      <c r="B273" t="n">
-        <v>1</v>
-      </c>
+      <c r="B273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
         <v>13686110392</v>
       </c>
-      <c r="B274" t="n">
-        <v>1</v>
-      </c>
+      <c r="B274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
         <v>13686144095</v>
       </c>
-      <c r="B275" t="n">
-        <v>0</v>
-      </c>
+      <c r="B275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
         <v>13686213715</v>
       </c>
-      <c r="B276" t="n">
-        <v>1</v>
-      </c>
+      <c r="B276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
         <v>13686216306</v>
       </c>
-      <c r="B277" t="n">
-        <v>0</v>
-      </c>
+      <c r="B277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
         <v>13686601052</v>
       </c>
-      <c r="B278" t="n">
-        <v>0</v>
-      </c>
+      <c r="B278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
         <v>13686601655</v>
       </c>
-      <c r="B279" t="n">
-        <v>1</v>
-      </c>
+      <c r="B279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
         <v>13686695138</v>
       </c>
-      <c r="B280" t="n">
-        <v>0</v>
-      </c>
+      <c r="B280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
         <v>13694912028</v>
       </c>
-      <c r="B281" t="n">
-        <v>1</v>
-      </c>
+      <c r="B281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
         <v>13694941815</v>
       </c>
-      <c r="B282" t="n">
-        <v>0</v>
-      </c>
+      <c r="B282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
         <v>13694997368</v>
       </c>
-      <c r="B283" t="n">
-        <v>0</v>
-      </c>
+      <c r="B283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
         <v>13711812362</v>
       </c>
-      <c r="B284" t="n">
-        <v>0</v>
-      </c>
+      <c r="B284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
         <v>13711873141</v>
       </c>
-      <c r="B285" t="n">
-        <v>1</v>
-      </c>
+      <c r="B285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
         <v>13711877045</v>
       </c>
-      <c r="B286" t="n">
-        <v>1</v>
-      </c>
+      <c r="B286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
         <v>13711879718</v>
       </c>
-      <c r="B287" t="n">
-        <v>1</v>
-      </c>
+      <c r="B287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
         <v>13711894720</v>
       </c>
-      <c r="B288" t="n">
-        <v>0</v>
-      </c>
+      <c r="B288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
         <v>13711896171</v>
       </c>
-      <c r="B289" t="n">
-        <v>0</v>
-      </c>
+      <c r="B289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
         <v>13711930666</v>
       </c>
-      <c r="B290" t="n">
-        <v>0</v>
-      </c>
+      <c r="B290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
         <v>13711936262</v>
       </c>
-      <c r="B291" t="n">
-        <v>0</v>
-      </c>
+      <c r="B291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
         <v>13711968145</v>
       </c>
-      <c r="B292" t="n">
-        <v>0</v>
-      </c>
+      <c r="B292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
         <v>13711977757</v>
       </c>
-      <c r="B293" t="n">
-        <v>0</v>
-      </c>
+      <c r="B293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
         <v>13711984987</v>
       </c>
-      <c r="B294" t="n">
-        <v>0</v>
-      </c>
+      <c r="B294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
         <v>13711991951</v>
       </c>
-      <c r="B295" t="n">
-        <v>1</v>
-      </c>
+      <c r="B295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
         <v>13711993776</v>
       </c>
-      <c r="B296" t="n">
-        <v>1</v>
-      </c>
+      <c r="B296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
         <v>13712019467</v>
       </c>
-      <c r="B297" t="n">
-        <v>0</v>
-      </c>
+      <c r="B297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
         <v>13712052155</v>
       </c>
-      <c r="B298" t="n">
-        <v>1</v>
-      </c>
+      <c r="B298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
         <v>13712096023</v>
       </c>
-      <c r="B299" t="n">
-        <v>0</v>
-      </c>
+      <c r="B299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
         <v>13712112289</v>
       </c>
-      <c r="B300" t="n">
-        <v>1</v>
-      </c>
+      <c r="B300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
         <v>13712226612</v>
       </c>
-      <c r="B301" t="n">
-        <v>0</v>
-      </c>
+      <c r="B301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
         <v>13712263752</v>
       </c>
-      <c r="B302" t="n">
-        <v>0</v>
-      </c>
+      <c r="B302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
         <v>13712268749</v>
       </c>
-      <c r="B303" t="n">
-        <v>0</v>
-      </c>
+      <c r="B303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
         <v>13712280944</v>
       </c>
-      <c r="B304" t="n">
-        <v>0</v>
-      </c>
+      <c r="B304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
         <v>13712291786</v>
       </c>
-      <c r="B305" t="n">
-        <v>1</v>
-      </c>
+      <c r="B305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
         <v>13712299996</v>
       </c>
-      <c r="B306" t="n">
-        <v>1</v>
-      </c>
+      <c r="B306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
         <v>13712320699</v>
       </c>
-      <c r="B307" t="n">
-        <v>1</v>
-      </c>
+      <c r="B307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
         <v>13712344703</v>
       </c>
-      <c r="B308" t="n">
-        <v>0</v>
-      </c>
+      <c r="B308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
         <v>13712353422</v>
       </c>
-      <c r="B309" t="n">
-        <v>1</v>
-      </c>
+      <c r="B309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
         <v>13712355082</v>
       </c>
-      <c r="B310" t="n">
-        <v>1</v>
-      </c>
+      <c r="B310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
         <v>13712355738</v>
       </c>
-      <c r="B311" t="n">
-        <v>0</v>
-      </c>
+      <c r="B311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
         <v>13712389828</v>
       </c>
-      <c r="B312" t="n">
-        <v>1</v>
-      </c>
+      <c r="B312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
         <v>13712449158</v>
       </c>
-      <c r="B313" t="n">
-        <v>0</v>
-      </c>
+      <c r="B313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
         <v>13712452369</v>
       </c>
-      <c r="B314" t="n">
-        <v>0</v>
-      </c>
+      <c r="B314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
         <v>13712516068</v>
       </c>
-      <c r="B315" t="n">
-        <v>1</v>
-      </c>
+      <c r="B315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
         <v>13712558108</v>
       </c>
-      <c r="B316" t="n">
-        <v>1</v>
-      </c>
+      <c r="B316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
         <v>13712586603</v>
       </c>
-      <c r="B317" t="n">
-        <v>1</v>
-      </c>
+      <c r="B317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
         <v>13712619108</v>
       </c>
-      <c r="B318" t="n">
-        <v>1</v>
-      </c>
+      <c r="B318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
         <v>13712662691</v>
       </c>
-      <c r="B319" t="n">
-        <v>1</v>
-      </c>
+      <c r="B319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
         <v>13712699109</v>
       </c>
-      <c r="B320" t="n">
-        <v>0</v>
-      </c>
+      <c r="B320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
         <v>13712723949</v>
       </c>
-      <c r="B321" t="n">
-        <v>0</v>
-      </c>
+      <c r="B321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
         <v>13712733431</v>
       </c>
-      <c r="B322" t="n">
-        <v>0</v>
-      </c>
+      <c r="B322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
         <v>13712733600</v>
       </c>
-      <c r="B323" t="n">
-        <v>1</v>
-      </c>
+      <c r="B323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
         <v>13712743010</v>
       </c>
-      <c r="B324" t="n">
-        <v>1</v>
-      </c>
+      <c r="B324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
         <v>13712765119</v>
       </c>
-      <c r="B325" t="n">
-        <v>1</v>
-      </c>
+      <c r="B325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
         <v>13712815826</v>
       </c>
-      <c r="B326" t="n">
-        <v>1</v>
-      </c>
+      <c r="B326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
         <v>13712839586</v>
       </c>
-      <c r="B327" t="n">
-        <v>0</v>
-      </c>
+      <c r="B327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
         <v>13712855578</v>
       </c>
-      <c r="B328" t="n">
-        <v>0</v>
-      </c>
+      <c r="B328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
         <v>13712872847</v>
       </c>
-      <c r="B329" t="n">
-        <v>1</v>
-      </c>
+      <c r="B329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
         <v>13712904380</v>
       </c>
-      <c r="B330" t="n">
-        <v>0</v>
-      </c>
+      <c r="B330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
         <v>13712998075</v>
       </c>
-      <c r="B331" t="n">
-        <v>0</v>
-      </c>
+      <c r="B331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
         <v>13713003738</v>
       </c>
-      <c r="B332" t="n">
-        <v>1</v>
-      </c>
+      <c r="B332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
         <v>13713074257</v>
       </c>
-      <c r="B333" t="n">
-        <v>1</v>
-      </c>
+      <c r="B333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
         <v>13713086699</v>
       </c>
-      <c r="B334" t="n">
-        <v>1</v>
-      </c>
+      <c r="B334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
         <v>13713115909</v>
       </c>
-      <c r="B335" t="n">
-        <v>1</v>
-      </c>
+      <c r="B335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
         <v>13713136083</v>
       </c>
-      <c r="B336" t="n">
-        <v>1</v>
-      </c>
+      <c r="B336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
         <v>13713198390</v>
       </c>
-      <c r="B337" t="n">
-        <v>0</v>
-      </c>
+      <c r="B337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
         <v>13713198711</v>
       </c>
-      <c r="B338" t="n">
-        <v>0</v>
-      </c>
+      <c r="B338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
         <v>13713204685</v>
       </c>
-      <c r="B339" t="n">
-        <v>0</v>
-      </c>
+      <c r="B339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
         <v>13713223897</v>
       </c>
-      <c r="B340" t="n">
-        <v>1</v>
-      </c>
+      <c r="B340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
         <v>13713308329</v>
       </c>
-      <c r="B341" t="n">
-        <v>1</v>
-      </c>
+      <c r="B341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
         <v>13713337846</v>
       </c>
-      <c r="B342" t="n">
-        <v>0</v>
-      </c>
+      <c r="B342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
         <v>13713409077</v>
       </c>
-      <c r="B343" t="n">
-        <v>1</v>
-      </c>
+      <c r="B343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
         <v>13713434111</v>
       </c>
-      <c r="B344" t="n">
-        <v>0</v>
-      </c>
+      <c r="B344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
         <v>13713444007</v>
       </c>
-      <c r="B345" t="n">
-        <v>1</v>
-      </c>
+      <c r="B345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
         <v>13717151972</v>
       </c>
-      <c r="B346" t="n">
-        <v>0</v>
-      </c>
+      <c r="B346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
         <v>13717307240</v>
       </c>
-      <c r="B347" t="n">
-        <v>1</v>
-      </c>
+      <c r="B347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
         <v>13717383282</v>
       </c>
-      <c r="B348" t="n">
-        <v>1</v>
-      </c>
+      <c r="B348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
         <v>13723500388</v>
       </c>
-      <c r="B349" t="n">
-        <v>1</v>
-      </c>
+      <c r="B349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
         <v>13723510133</v>
       </c>
-      <c r="B350" t="n">
-        <v>1</v>
-      </c>
+      <c r="B350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
         <v>13723558415</v>
       </c>
-      <c r="B351" t="n">
-        <v>1</v>
-      </c>
+      <c r="B351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
         <v>13723569673</v>
       </c>
-      <c r="B352" t="n">
-        <v>0</v>
-      </c>
+      <c r="B352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
         <v>13723596261</v>
       </c>
-      <c r="B353" t="n">
-        <v>0</v>
-      </c>
+      <c r="B353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
         <v>13724439128</v>
       </c>
-      <c r="B354" t="n">
-        <v>0</v>
-      </c>
+      <c r="B354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
         <v>13724450035</v>
       </c>
-      <c r="B355" t="n">
-        <v>0</v>
-      </c>
+      <c r="B355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
         <v>13724464119</v>
       </c>
-      <c r="B356" t="n">
-        <v>1</v>
-      </c>
+      <c r="B356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
         <v>13724479441</v>
       </c>
-      <c r="B357" t="n">
-        <v>0</v>
-      </c>
+      <c r="B357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
         <v>13725707485</v>
       </c>
-      <c r="B358" t="n">
-        <v>0</v>
-      </c>
+      <c r="B358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
         <v>13725800358</v>
       </c>
-      <c r="B359" t="n">
-        <v>1</v>
-      </c>
+      <c r="B359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
         <v>13725826806</v>
       </c>
-      <c r="B360" t="n">
-        <v>0</v>
-      </c>
+      <c r="B360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
         <v>13726417549</v>
       </c>
-      <c r="B361" t="n">
-        <v>1</v>
-      </c>
+      <c r="B361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
         <v>13726442133</v>
       </c>
-      <c r="B362" t="n">
-        <v>0</v>
-      </c>
+      <c r="B362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
         <v>13726498649</v>
       </c>
-      <c r="B363" t="n">
-        <v>1</v>
-      </c>
+      <c r="B363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
         <v>13728149426</v>
       </c>
-      <c r="B364" t="n">
-        <v>0</v>
-      </c>
+      <c r="B364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
         <v>13728151231</v>
       </c>
-      <c r="B365" t="n">
-        <v>1</v>
-      </c>
+      <c r="B365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
         <v>13728163275</v>
       </c>
-      <c r="B366" t="n">
-        <v>0</v>
-      </c>
+      <c r="B366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
         <v>13728185013</v>
       </c>
-      <c r="B367" t="n">
-        <v>1</v>
-      </c>
+      <c r="B367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
         <v>13728204165</v>
       </c>
-      <c r="B368" t="n">
-        <v>1</v>
-      </c>
+      <c r="B368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
         <v>13728219490</v>
       </c>
-      <c r="B369" t="n">
-        <v>0</v>
-      </c>
+      <c r="B369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
         <v>13728236582</v>
       </c>
-      <c r="B370" t="n">
-        <v>1</v>
-      </c>
+      <c r="B370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
         <v>13728240079</v>
       </c>
-      <c r="B371" t="n">
-        <v>0</v>
-      </c>
+      <c r="B371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
         <v>13728327228</v>
       </c>
-      <c r="B372" t="n">
-        <v>1</v>
-      </c>
+      <c r="B372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
         <v>13728341239</v>
       </c>
-      <c r="B373" t="n">
-        <v>1</v>
-      </c>
+      <c r="B373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
         <v>13728390010</v>
       </c>
-      <c r="B374" t="n">
-        <v>1</v>
-      </c>
+      <c r="B374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
         <v>13728411491</v>
       </c>
-      <c r="B375" t="n">
-        <v>0</v>
-      </c>
+      <c r="B375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
         <v>13728452399</v>
       </c>
-      <c r="B376" t="n">
-        <v>1</v>
-      </c>
+      <c r="B376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
         <v>13728483197</v>
       </c>
-      <c r="B377" t="n">
-        <v>0</v>
-      </c>
+      <c r="B377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
         <v>13729920018</v>
       </c>
-      <c r="B378" t="n">
-        <v>0</v>
-      </c>
+      <c r="B378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
         <v>13729921556</v>
       </c>
-      <c r="B379" t="n">
-        <v>1</v>
-      </c>
+      <c r="B379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
         <v>13729956831</v>
       </c>
-      <c r="B380" t="n">
-        <v>0</v>
-      </c>
+      <c r="B380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
         <v>13729983984</v>
       </c>
-      <c r="B381" t="n">
-        <v>1</v>
-      </c>
+      <c r="B381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
         <v>13751234067</v>
       </c>
-      <c r="B382" t="n">
-        <v>0</v>
-      </c>
+      <c r="B382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
         <v>13751271392</v>
       </c>
-      <c r="B383" t="n">
-        <v>1</v>
-      </c>
+      <c r="B383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
         <v>13751272740</v>
       </c>
-      <c r="B384" t="n">
-        <v>0</v>
-      </c>
+      <c r="B384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
         <v>13751274207</v>
       </c>
-      <c r="B385" t="n">
-        <v>1</v>
-      </c>
+      <c r="B385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
         <v>13751293361</v>
       </c>
-      <c r="B386" t="n">
-        <v>1</v>
-      </c>
+      <c r="B386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
         <v>13751419235</v>
       </c>
-      <c r="B387" t="n">
-        <v>1</v>
-      </c>
+      <c r="B387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
         <v>13763174190</v>
       </c>
-      <c r="B388" t="n">
-        <v>0</v>
-      </c>
+      <c r="B388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
         <v>13763175212</v>
       </c>
-      <c r="B389" t="n">
-        <v>0</v>
-      </c>
+      <c r="B389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
         <v>13763193133</v>
       </c>
-      <c r="B390" t="n">
-        <v>1</v>
-      </c>
+      <c r="B390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
         <v>13763220454</v>
       </c>
-      <c r="B391" t="n">
-        <v>0</v>
-      </c>
+      <c r="B391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
         <v>13763231696</v>
       </c>
-      <c r="B392" t="n">
-        <v>1</v>
-      </c>
+      <c r="B392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
         <v>13790136902</v>
       </c>
-      <c r="B393" t="n">
-        <v>1</v>
-      </c>
+      <c r="B393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
         <v>13790155991</v>
       </c>
-      <c r="B394" t="n">
-        <v>0</v>
-      </c>
+      <c r="B394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
         <v>13790159430</v>
       </c>
-      <c r="B395" t="n">
-        <v>0</v>
-      </c>
+      <c r="B395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
         <v>13790222165</v>
       </c>
-      <c r="B396" t="n">
-        <v>0</v>
-      </c>
+      <c r="B396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
         <v>13790252808</v>
       </c>
-      <c r="B397" t="n">
-        <v>1</v>
-      </c>
+      <c r="B397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
         <v>13790296326</v>
       </c>
-      <c r="B398" t="n">
-        <v>0</v>
-      </c>
+      <c r="B398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
         <v>13790313316</v>
       </c>
-      <c r="B399" t="n">
-        <v>1</v>
-      </c>
+      <c r="B399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
         <v>13790319372</v>
       </c>
-      <c r="B400" t="n">
-        <v>0</v>
-      </c>
+      <c r="B400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
         <v>13790352650</v>
       </c>
-      <c r="B401" t="n">
-        <v>1</v>
-      </c>
+      <c r="B401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
         <v>13790371035</v>
       </c>
-      <c r="B402" t="n">
-        <v>0</v>
-      </c>
+      <c r="B402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
         <v>13790393954</v>
       </c>
-      <c r="B403" t="n">
-        <v>0</v>
-      </c>
+      <c r="B403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
         <v>13790405589</v>
       </c>
-      <c r="B404" t="n">
-        <v>0</v>
-      </c>
+      <c r="B404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
         <v>13790419056</v>
       </c>
-      <c r="B405" t="n">
-        <v>0</v>
-      </c>
+      <c r="B405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
         <v>13790421095</v>
       </c>
-      <c r="B406" t="n">
-        <v>0</v>
-      </c>
+      <c r="B406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
         <v>13790458353</v>
       </c>
-      <c r="B407" t="n">
-        <v>1</v>
-      </c>
+      <c r="B407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
         <v>13790483302</v>
       </c>
-      <c r="B408" t="n">
-        <v>1</v>
-      </c>
+      <c r="B408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
         <v>13790494488</v>
       </c>
-      <c r="B409" t="n">
-        <v>1</v>
-      </c>
+      <c r="B409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
         <v>13790494902</v>
       </c>
-      <c r="B410" t="n">
-        <v>0</v>
-      </c>
+      <c r="B410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
         <v>13790578973</v>
       </c>
-      <c r="B411" t="n">
-        <v>0</v>
-      </c>
+      <c r="B411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
         <v>13790601572</v>
       </c>
-      <c r="B412" t="n">
-        <v>1</v>
-      </c>
+      <c r="B412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
         <v>13790683138</v>
       </c>
-      <c r="B413" t="n">
-        <v>1</v>
-      </c>
+      <c r="B413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
         <v>13790687776</v>
       </c>
-      <c r="B414" t="n">
-        <v>0</v>
-      </c>
+      <c r="B414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
         <v>13790689947</v>
       </c>
-      <c r="B415" t="n">
-        <v>1</v>
-      </c>
+      <c r="B415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
         <v>13790691705</v>
       </c>
-      <c r="B416" t="n">
-        <v>0</v>
-      </c>
+      <c r="B416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
         <v>13794868255</v>
       </c>
-      <c r="B417" t="n">
-        <v>0</v>
-      </c>
+      <c r="B417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
         <v>13794949764</v>
       </c>
-      <c r="B418" t="n">
-        <v>0</v>
-      </c>
+      <c r="B418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
         <v>13798781472</v>
       </c>
-      <c r="B419" t="n">
-        <v>0</v>
-      </c>
+      <c r="B419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
         <v>13798781690</v>
       </c>
-      <c r="B420" t="n">
-        <v>0</v>
-      </c>
+      <c r="B420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
         <v>13798823821</v>
       </c>
-      <c r="B421" t="n">
-        <v>0</v>
-      </c>
+      <c r="B421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
         <v>13798843237</v>
       </c>
-      <c r="B422" t="n">
-        <v>1</v>
-      </c>
+      <c r="B422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
         <v>13798855625</v>
       </c>
-      <c r="B423" t="n">
-        <v>1</v>
-      </c>
+      <c r="B423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
         <v>13798856719</v>
       </c>
-      <c r="B424" t="n">
-        <v>0</v>
-      </c>
+      <c r="B424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
         <v>13798881331</v>
       </c>
-      <c r="B425" t="n">
-        <v>0</v>
-      </c>
+      <c r="B425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
         <v>13798895886</v>
       </c>
-      <c r="B426" t="n">
-        <v>1</v>
-      </c>
+      <c r="B426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
         <v>13798896320</v>
       </c>
-      <c r="B427" t="n">
-        <v>1</v>
-      </c>
+      <c r="B427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
         <v>13798898561</v>
       </c>
-      <c r="B428" t="n">
-        <v>1</v>
-      </c>
+      <c r="B428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
         <v>13798930665</v>
       </c>
-      <c r="B429" t="n">
-        <v>1</v>
-      </c>
+      <c r="B429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
         <v>13798933533</v>
       </c>
-      <c r="B430" t="n">
-        <v>1</v>
-      </c>
+      <c r="B430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
         <v>13802386445</v>
       </c>
-      <c r="B431" t="n">
-        <v>0</v>
-      </c>
+      <c r="B431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
         <v>13802397109</v>
       </c>
-      <c r="B432" t="n">
-        <v>1</v>
-      </c>
+      <c r="B432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
         <v>13809616372</v>
       </c>
-      <c r="B433" t="n">
-        <v>0</v>
-      </c>
+      <c r="B433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
         <v>13809619132</v>
       </c>
-      <c r="B434" t="n">
-        <v>1</v>
-      </c>
+      <c r="B434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
         <v>13809644011</v>
       </c>
-      <c r="B435" t="n">
-        <v>0</v>
-      </c>
+      <c r="B435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
         <v>13809827203</v>
       </c>
-      <c r="B436" t="n">
-        <v>1</v>
-      </c>
+      <c r="B436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
         <v>13825720922</v>
       </c>
-      <c r="B437" t="n">
-        <v>0</v>
-      </c>
+      <c r="B437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
         <v>13825730587</v>
       </c>
-      <c r="B438" t="n">
-        <v>1</v>
-      </c>
+      <c r="B438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
         <v>13825764627</v>
       </c>
-      <c r="B439" t="n">
-        <v>1</v>
-      </c>
+      <c r="B439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
         <v>13825778943</v>
       </c>
-      <c r="B440" t="n">
-        <v>0</v>
-      </c>
+      <c r="B440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
         <v>13825780799</v>
       </c>
-      <c r="B441" t="n">
-        <v>0</v>
-      </c>
+      <c r="B441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
         <v>13826944862</v>
       </c>
-      <c r="B442" t="n">
-        <v>0</v>
-      </c>
+      <c r="B442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
         <v>13826958639</v>
       </c>
-      <c r="B443" t="n">
-        <v>0</v>
-      </c>
+      <c r="B443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
         <v>13826985060</v>
       </c>
-      <c r="B444" t="n">
-        <v>1</v>
-      </c>
+      <c r="B444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
         <v>13827230263</v>
       </c>
-      <c r="B445" t="n">
-        <v>1</v>
-      </c>
+      <c r="B445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
         <v>13827244150</v>
       </c>
-      <c r="B446" t="n">
-        <v>1</v>
-      </c>
+      <c r="B446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
         <v>13827244258</v>
       </c>
-      <c r="B447" t="n">
-        <v>0</v>
-      </c>
+      <c r="B447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
         <v>13827244347</v>
       </c>
-      <c r="B448" t="n">
-        <v>1</v>
-      </c>
+      <c r="B448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
         <v>13827247099</v>
       </c>
-      <c r="B449" t="n">
-        <v>1</v>
-      </c>
+      <c r="B449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
         <v>13827279440</v>
       </c>
-      <c r="B450" t="n">
-        <v>1</v>
-      </c>
+      <c r="B450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
         <v>13827299884</v>
       </c>
-      <c r="B451" t="n">
-        <v>0</v>
-      </c>
+      <c r="B451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
         <v>13829118773</v>
       </c>
-      <c r="B452" t="n">
-        <v>0</v>
-      </c>
+      <c r="B452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
         <v>13829134489</v>
       </c>
-      <c r="B453" t="n">
-        <v>1</v>
-      </c>
+      <c r="B453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
         <v>13829159456</v>
       </c>
-      <c r="B454" t="n">
-        <v>0</v>
-      </c>
+      <c r="B454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
         <v>13829220547</v>
       </c>
-      <c r="B455" t="n">
-        <v>0</v>
-      </c>
+      <c r="B455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
         <v>13829225427</v>
       </c>
-      <c r="B456" t="n">
-        <v>0</v>
-      </c>
+      <c r="B456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
         <v>13829233780</v>
       </c>
-      <c r="B457" t="n">
-        <v>1</v>
-      </c>
+      <c r="B457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
         <v>13829250308</v>
       </c>
-      <c r="B458" t="n">
-        <v>1</v>
-      </c>
+      <c r="B458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
         <v>13829252724</v>
       </c>
-      <c r="B459" t="n">
-        <v>1</v>
-      </c>
+      <c r="B459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
         <v>13829253711</v>
       </c>
-      <c r="B460" t="n">
-        <v>1</v>
-      </c>
+      <c r="B460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
         <v>13829269116</v>
       </c>
-      <c r="B461" t="n">
-        <v>1</v>
-      </c>
+      <c r="B461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
         <v>13829283209</v>
       </c>
-      <c r="B462" t="n">
-        <v>0</v>
-      </c>
+      <c r="B462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
         <v>13902605162</v>
       </c>
-      <c r="B463" t="n">
-        <v>1</v>
-      </c>
+      <c r="B463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
         <v>13902615601</v>
       </c>
-      <c r="B464" t="n">
-        <v>0</v>
-      </c>
+      <c r="B464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
         <v>13902646515</v>
       </c>
-      <c r="B465" t="n">
-        <v>0</v>
-      </c>
+      <c r="B465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
         <v>13903034038</v>
       </c>
-      <c r="B466" t="n">
-        <v>1</v>
-      </c>
+      <c r="B466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
         <v>13922535233</v>
       </c>
-      <c r="B467" t="n">
-        <v>1</v>
-      </c>
+      <c r="B467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
         <v>13922909248</v>
       </c>
-      <c r="B468" t="n">
-        <v>0</v>
-      </c>
+      <c r="B468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
         <v>13922920808</v>
       </c>
-      <c r="B469" t="n">
-        <v>1</v>
-      </c>
+      <c r="B469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
         <v>13922954099</v>
       </c>
-      <c r="B470" t="n">
-        <v>0</v>
-      </c>
+      <c r="B470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
         <v>13922963288</v>
       </c>
-      <c r="B471" t="n">
-        <v>1</v>
-      </c>
+      <c r="B471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
         <v>13922969663</v>
       </c>
-      <c r="B472" t="n">
-        <v>0</v>
-      </c>
+      <c r="B472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
         <v>13924338129</v>
       </c>
-      <c r="B473" t="n">
-        <v>0</v>
-      </c>
+      <c r="B473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
         <v>13924338938</v>
       </c>
-      <c r="B474" t="n">
-        <v>0</v>
-      </c>
+      <c r="B474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
         <v>13924352371</v>
       </c>
-      <c r="B475" t="n">
-        <v>0</v>
-      </c>
+      <c r="B475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
         <v>13924364713</v>
       </c>
-      <c r="B476" t="n">
-        <v>1</v>
-      </c>
+      <c r="B476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
         <v>13925503695</v>
       </c>
-      <c r="B477" t="n">
-        <v>1</v>
-      </c>
+      <c r="B477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
         <v>13925513168</v>
       </c>
-      <c r="B478" t="n">
-        <v>1</v>
-      </c>
+      <c r="B478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
         <v>13925560363</v>
       </c>
-      <c r="B479" t="n">
-        <v>1</v>
-      </c>
+      <c r="B479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
         <v>13925569861</v>
       </c>
-      <c r="B480" t="n">
-        <v>0</v>
-      </c>
+      <c r="B480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
         <v>13925583326</v>
       </c>
-      <c r="B481" t="n">
-        <v>1</v>
-      </c>
+      <c r="B481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
         <v>13925705688</v>
       </c>
-      <c r="B482" t="n">
-        <v>0</v>
-      </c>
+      <c r="B482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
         <v>13925718972</v>
       </c>
-      <c r="B483" t="n">
-        <v>0</v>
-      </c>
+      <c r="B483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
         <v>13925730397</v>
       </c>
-      <c r="B484" t="n">
-        <v>0</v>
-      </c>
+      <c r="B484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
         <v>13925760616</v>
       </c>
-      <c r="B485" t="n">
-        <v>1</v>
-      </c>
+      <c r="B485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
         <v>13925771228</v>
       </c>
-      <c r="B486" t="n">
-        <v>1</v>
-      </c>
+      <c r="B486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
         <v>13925771790</v>
       </c>
-      <c r="B487" t="n">
-        <v>0</v>
-      </c>
+      <c r="B487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
         <v>13925843386</v>
       </c>
-      <c r="B488" t="n">
-        <v>1</v>
-      </c>
+      <c r="B488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
         <v>13925888518</v>
       </c>
-      <c r="B489" t="n">
-        <v>1</v>
-      </c>
+      <c r="B489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
         <v>13926804679</v>
       </c>
-      <c r="B490" t="n">
-        <v>1</v>
-      </c>
+      <c r="B490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
         <v>13926812360</v>
       </c>
-      <c r="B491" t="n">
-        <v>0</v>
-      </c>
+      <c r="B491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
         <v>13926873805</v>
       </c>
-      <c r="B492" t="n">
-        <v>1</v>
-      </c>
+      <c r="B492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
         <v>13929201550</v>
       </c>
-      <c r="B493" t="n">
-        <v>0</v>
-      </c>
+      <c r="B493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
         <v>13929215076</v>
       </c>
-      <c r="B494" t="n">
-        <v>1</v>
-      </c>
+      <c r="B494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
         <v>13929228563</v>
       </c>
-      <c r="B495" t="n">
-        <v>0</v>
-      </c>
+      <c r="B495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
         <v>13929247995</v>
       </c>
-      <c r="B496" t="n">
-        <v>0</v>
-      </c>
+      <c r="B496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
         <v>13929276298</v>
       </c>
-      <c r="B497" t="n">
-        <v>1</v>
-      </c>
+      <c r="B497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
         <v>13929279018</v>
       </c>
-      <c r="B498" t="n">
-        <v>1</v>
-      </c>
+      <c r="B498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
         <v>13929283191</v>
       </c>
-      <c r="B499" t="n">
-        <v>1</v>
-      </c>
+      <c r="B499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
         <v>13929441962</v>
       </c>
-      <c r="B500" t="n">
-        <v>1</v>
-      </c>
+      <c r="B500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
         <v>13929474685</v>
       </c>
-      <c r="B501" t="n">
-        <v>1</v>
-      </c>
+      <c r="B501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
         <v>14707616466</v>
       </c>
-      <c r="B502" t="n">
-        <v>0</v>
-      </c>
+      <c r="B502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
         <v>14716177455</v>
       </c>
-      <c r="B503" t="n">
-        <v>0</v>
-      </c>
+      <c r="B503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
         <v>14778641467</v>
       </c>
-      <c r="B504" t="n">
-        <v>0</v>
-      </c>
+      <c r="B504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
         <v>15007690545</v>
       </c>
-      <c r="B505" t="n">
-        <v>0</v>
-      </c>
+      <c r="B505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
         <v>15014875182</v>
       </c>
-      <c r="B506" t="n">
-        <v>0</v>
-      </c>
+      <c r="B506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
         <v>15014880970</v>
       </c>
-      <c r="B507" t="n">
-        <v>1</v>
-      </c>
+      <c r="B507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
         <v>15015110519</v>
       </c>
-      <c r="B508" t="n">
-        <v>0</v>
-      </c>
+      <c r="B508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
         <v>15015148634</v>
       </c>
-      <c r="B509" t="n">
-        <v>0</v>
-      </c>
+      <c r="B509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
         <v>15015157762</v>
       </c>
-      <c r="B510" t="n">
-        <v>1</v>
-      </c>
+      <c r="B510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
         <v>15015315631</v>
       </c>
-      <c r="B511" t="n">
-        <v>0</v>
-      </c>
+      <c r="B511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
         <v>15015325567</v>
       </c>
-      <c r="B512" t="n">
-        <v>0</v>
-      </c>
+      <c r="B512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
         <v>15015348580</v>
       </c>
-      <c r="B513" t="n">
-        <v>0</v>
-      </c>
+      <c r="B513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
         <v>15015370313</v>
       </c>
-      <c r="B514" t="n">
-        <v>0</v>
-      </c>
+      <c r="B514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
         <v>15015385461</v>
       </c>
-      <c r="B515" t="n">
-        <v>0</v>
-      </c>
+      <c r="B515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
         <v>15015385723</v>
       </c>
-      <c r="B516" t="n">
-        <v>0</v>
-      </c>
+      <c r="B516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
         <v>15015388412</v>
       </c>
-      <c r="B517" t="n">
-        <v>0</v>
-      </c>
+      <c r="B517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
         <v>15015419780</v>
       </c>
-      <c r="B518" t="n">
-        <v>0</v>
-      </c>
+      <c r="B518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
         <v>15015450642</v>
       </c>
-      <c r="B519" t="n">
-        <v>0</v>
-      </c>
+      <c r="B519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
         <v>15016775470</v>
       </c>
-      <c r="B520" t="n">
-        <v>0</v>
-      </c>
+      <c r="B520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
         <v>15016775542</v>
       </c>
-      <c r="B521" t="n">
-        <v>0</v>
-      </c>
+      <c r="B521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
         <v>15016776574</v>
       </c>
-      <c r="B522" t="n">
-        <v>0</v>
-      </c>
+      <c r="B522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
         <v>15016779196</v>
       </c>
-      <c r="B523" t="n">
-        <v>0</v>
-      </c>
+      <c r="B523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
         <v>15016783174</v>
       </c>
-      <c r="B524" t="n">
-        <v>0</v>
-      </c>
+      <c r="B524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
         <v>15016849818</v>
       </c>
-      <c r="B525" t="n">
-        <v>1</v>
-      </c>
+      <c r="B525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
         <v>15016853982</v>
       </c>
-      <c r="B526" t="n">
-        <v>0</v>
-      </c>
+      <c r="B526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
         <v>15016954375</v>
       </c>
-      <c r="B527" t="n">
-        <v>1</v>
-      </c>
+      <c r="B527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
         <v>15016968735</v>
       </c>
-      <c r="B528" t="n">
-        <v>0</v>
-      </c>
+      <c r="B528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
         <v>15017065662</v>
       </c>
-      <c r="B529" t="n">
-        <v>0</v>
-      </c>
+      <c r="B529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
         <v>15017076023</v>
       </c>
-      <c r="B530" t="n">
-        <v>0</v>
-      </c>
+      <c r="B530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
         <v>15017143265</v>
       </c>
-      <c r="B531" t="n">
-        <v>1</v>
-      </c>
+      <c r="B531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
         <v>15017158272</v>
       </c>
-      <c r="B532" t="n">
-        <v>0</v>
-      </c>
+      <c r="B532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
         <v>15017850411</v>
       </c>
-      <c r="B533" t="n">
-        <v>0</v>
-      </c>
+      <c r="B533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
         <v>15017883106</v>
       </c>
-      <c r="B534" t="n">
-        <v>1</v>
-      </c>
+      <c r="B534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
         <v>15019002825</v>
       </c>
-      <c r="B535" t="n">
-        <v>0</v>
-      </c>
+      <c r="B535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
         <v>15019004181</v>
       </c>
-      <c r="B536" t="n">
-        <v>1</v>
-      </c>
+      <c r="B536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
         <v>15019119782</v>
       </c>
-      <c r="B537" t="n">
-        <v>1</v>
-      </c>
+      <c r="B537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
         <v>15019168048</v>
       </c>
-      <c r="B538" t="n">
-        <v>0</v>
-      </c>
+      <c r="B538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
         <v>15019961972</v>
       </c>
-      <c r="B539" t="n">
-        <v>0</v>
-      </c>
+      <c r="B539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
         <v>15019963656</v>
       </c>
-      <c r="B540" t="n">
-        <v>0</v>
-      </c>
+      <c r="B540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
         <v>15019983945</v>
       </c>
-      <c r="B541" t="n">
-        <v>0</v>
-      </c>
+      <c r="B541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
         <v>15019987392</v>
       </c>
-      <c r="B542" t="n">
-        <v>1</v>
-      </c>
+      <c r="B542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
         <v>15019989607</v>
       </c>
-      <c r="B543" t="n">
-        <v>0</v>
-      </c>
+      <c r="B543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
         <v>15024022860</v>
       </c>
-      <c r="B544" t="n">
-        <v>0</v>
-      </c>
+      <c r="B544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
         <v>15024169015</v>
       </c>
-      <c r="B545" t="n">
-        <v>1</v>
-      </c>
+      <c r="B545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
         <v>15099714814</v>
       </c>
-      <c r="B546" t="n">
-        <v>0</v>
-      </c>
+      <c r="B546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
         <v>15099722917</v>
       </c>
-      <c r="B547" t="n">
-        <v>0</v>
-      </c>
+      <c r="B547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
         <v>15112786347</v>
       </c>
-      <c r="B548" t="n">
-        <v>0</v>
-      </c>
+      <c r="B548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
         <v>15112788834</v>
       </c>
-      <c r="B549" t="n">
-        <v>0</v>
-      </c>
+      <c r="B549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
         <v>15118204578</v>
       </c>
-      <c r="B550" t="n">
-        <v>0</v>
-      </c>
+      <c r="B550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
         <v>15118255586</v>
       </c>
-      <c r="B551" t="n">
-        <v>0</v>
-      </c>
+      <c r="B551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
         <v>15118280737</v>
       </c>
-      <c r="B552" t="n">
-        <v>1</v>
-      </c>
+      <c r="B552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
         <v>15118438320</v>
       </c>
-      <c r="B553" t="n">
-        <v>0</v>
-      </c>
+      <c r="B553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
         <v>15118462270</v>
       </c>
-      <c r="B554" t="n">
-        <v>0</v>
-      </c>
+      <c r="B554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
         <v>15118533191</v>
       </c>
-      <c r="B555" t="n">
-        <v>0</v>
-      </c>
+      <c r="B555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
         <v>15118551905</v>
       </c>
-      <c r="B556" t="n">
-        <v>0</v>
-      </c>
+      <c r="B556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
         <v>15217106101</v>
       </c>
-      <c r="B557" t="n">
-        <v>0</v>
-      </c>
+      <c r="B557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="n">
         <v>15217236545</v>
       </c>
-      <c r="B558" t="n">
-        <v>0</v>
-      </c>
+      <c r="B558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
         <v>15217251148</v>
       </c>
-      <c r="B559" t="n">
-        <v>0</v>
-      </c>
+      <c r="B559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
         <v>15217256381</v>
       </c>
-      <c r="B560" t="n">
-        <v>0</v>
-      </c>
+      <c r="B560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
         <v>15217536847</v>
       </c>
-      <c r="B561" t="n">
-        <v>0</v>
-      </c>
+      <c r="B561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
         <v>15218752704</v>
       </c>
-      <c r="B562" t="n">
-        <v>0</v>
-      </c>
+      <c r="B562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
         <v>15220296709</v>
       </c>
-      <c r="B563" t="n">
-        <v>0</v>
-      </c>
+      <c r="B563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
         <v>15220326653</v>
       </c>
-      <c r="B564" t="n">
-        <v>0</v>
-      </c>
+      <c r="B564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="n">
         <v>15220332826</v>
       </c>
-      <c r="B565" t="n">
-        <v>0</v>
-      </c>
+      <c r="B565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="n">
         <v>15220335349</v>
       </c>
-      <c r="B566" t="n">
-        <v>0</v>
-      </c>
+      <c r="B566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="n">
         <v>15220384233</v>
       </c>
-      <c r="B567" t="n">
-        <v>1</v>
-      </c>
+      <c r="B567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="n">
         <v>15724016772</v>
       </c>
-      <c r="B568" t="n">
-        <v>0</v>
-      </c>
+      <c r="B568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="n">
         <v>15728120848</v>
       </c>
-      <c r="B569" t="n">
-        <v>0</v>
-      </c>
+      <c r="B569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
         <v>15728133005</v>
       </c>
-      <c r="B570" t="n">
-        <v>0</v>
-      </c>
+      <c r="B570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="n">
         <v>15728138776</v>
       </c>
-      <c r="B571" t="n">
-        <v>0</v>
-      </c>
+      <c r="B571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="n">
         <v>15790452120</v>
       </c>
-      <c r="B572" t="n">
-        <v>0</v>
-      </c>
+      <c r="B572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="n">
         <v>15807692329</v>
       </c>
-      <c r="B573" t="n">
-        <v>1</v>
-      </c>
+      <c r="B573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="n">
         <v>15812810568</v>
       </c>
-      <c r="B574" t="n">
-        <v>1</v>
-      </c>
+      <c r="B574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
         <v>15814224987</v>
       </c>
-      <c r="B575" t="n">
-        <v>0</v>
-      </c>
+      <c r="B575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="n">
         <v>15814231903</v>
       </c>
-      <c r="B576" t="n">
-        <v>0</v>
-      </c>
+      <c r="B576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="n">
         <v>15814292949</v>
       </c>
-      <c r="B577" t="n">
-        <v>0</v>
-      </c>
+      <c r="B577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="n">
         <v>15816811227</v>
       </c>
-      <c r="B578" t="n">
-        <v>0</v>
-      </c>
+      <c r="B578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
         <v>15816827822</v>
       </c>
-      <c r="B579" t="n">
-        <v>1</v>
-      </c>
+      <c r="B579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
         <v>15816838490</v>
       </c>
-      <c r="B580" t="n">
-        <v>1</v>
-      </c>
+      <c r="B580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
         <v>15817534868</v>
       </c>
-      <c r="B581" t="n">
-        <v>1</v>
-      </c>
+      <c r="B581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
         <v>15817549270</v>
       </c>
-      <c r="B582" t="n">
-        <v>0</v>
-      </c>
+      <c r="B582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
         <v>15817674097</v>
       </c>
-      <c r="B583" t="n">
-        <v>0</v>
-      </c>
+      <c r="B583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
         <v>15817703818</v>
       </c>
-      <c r="B584" t="n">
-        <v>0</v>
-      </c>
+      <c r="B584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
         <v>15817710814</v>
       </c>
-      <c r="B585" t="n">
-        <v>0</v>
-      </c>
+      <c r="B585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
         <v>15817731091</v>
       </c>
-      <c r="B586" t="n">
-        <v>0</v>
-      </c>
+      <c r="B586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
         <v>15817748048</v>
       </c>
-      <c r="B587" t="n">
-        <v>1</v>
-      </c>
+      <c r="B587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
         <v>15817753386</v>
       </c>
-      <c r="B588" t="n">
-        <v>1</v>
-      </c>
+      <c r="B588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
         <v>15817772392</v>
       </c>
-      <c r="B589" t="n">
-        <v>1</v>
-      </c>
+      <c r="B589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
         <v>15817778626</v>
       </c>
-      <c r="B590" t="n">
-        <v>0</v>
-      </c>
+      <c r="B590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="n">
         <v>15818243519</v>
       </c>
-      <c r="B591" t="n">
-        <v>0</v>
-      </c>
+      <c r="B591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
         <v>15818266917</v>
       </c>
-      <c r="B592" t="n">
-        <v>0</v>
-      </c>
+      <c r="B592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
         <v>15818314036</v>
       </c>
-      <c r="B593" t="n">
-        <v>0</v>
-      </c>
+      <c r="B593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
         <v>15818321755</v>
       </c>
-      <c r="B594" t="n">
-        <v>1</v>
-      </c>
+      <c r="B594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
         <v>15818351451</v>
       </c>
-      <c r="B595" t="n">
-        <v>0</v>
-      </c>
+      <c r="B595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
         <v>15818383218</v>
       </c>
-      <c r="B596" t="n">
-        <v>1</v>
-      </c>
+      <c r="B596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
         <v>15818395126</v>
       </c>
-      <c r="B597" t="n">
-        <v>0</v>
-      </c>
+      <c r="B597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
         <v>15818449151</v>
       </c>
-      <c r="B598" t="n">
-        <v>0</v>
-      </c>
+      <c r="B598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="n">
         <v>15818449949</v>
       </c>
-      <c r="B599" t="n">
-        <v>0</v>
-      </c>
+      <c r="B599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
         <v>15820852256</v>
       </c>
-      <c r="B600" t="n">
-        <v>0</v>
-      </c>
+      <c r="B600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="n">
         <v>15820886548</v>
       </c>
-      <c r="B601" t="n">
-        <v>1</v>
-      </c>
+      <c r="B601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
         <v>15876417711</v>
       </c>
-      <c r="B602" t="n">
-        <v>0</v>
-      </c>
+      <c r="B602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
         <v>15899692258</v>
       </c>
-      <c r="B603" t="n">
-        <v>1</v>
-      </c>
+      <c r="B603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="n">
         <v>15899939920</v>
       </c>
-      <c r="B604" t="n">
-        <v>0</v>
-      </c>
+      <c r="B604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="n">
         <v>15913720570</v>
       </c>
-      <c r="B605" t="n">
-        <v>1</v>
-      </c>
+      <c r="B605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="n">
         <v>15913834502</v>
       </c>
-      <c r="B606" t="n">
-        <v>1</v>
-      </c>
+      <c r="B606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="n">
         <v>15916713329</v>
       </c>
-      <c r="B607" t="n">
-        <v>1</v>
-      </c>
+      <c r="B607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="n">
         <v>15916750954</v>
       </c>
-      <c r="B608" t="n">
-        <v>1</v>
-      </c>
+      <c r="B608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="n">
         <v>15916752520</v>
       </c>
-      <c r="B609" t="n">
-        <v>1</v>
-      </c>
+      <c r="B609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="n">
         <v>15916772379</v>
       </c>
-      <c r="B610" t="n">
-        <v>0</v>
-      </c>
+      <c r="B610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="n">
         <v>15916780621</v>
       </c>
-      <c r="B611" t="n">
-        <v>0</v>
-      </c>
+      <c r="B611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="n">
         <v>15916834038</v>
       </c>
-      <c r="B612" t="n">
-        <v>0</v>
-      </c>
+      <c r="B612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
         <v>15916848357</v>
       </c>
-      <c r="B613" t="n">
-        <v>0</v>
-      </c>
+      <c r="B613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
         <v>15916873383</v>
       </c>
-      <c r="B614" t="n">
-        <v>1</v>
-      </c>
+      <c r="B614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="n">
         <v>15916891272</v>
       </c>
-      <c r="B615" t="n">
-        <v>1</v>
-      </c>
+      <c r="B615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="n">
         <v>15916941618</v>
       </c>
-      <c r="B616" t="n">
-        <v>0</v>
-      </c>
+      <c r="B616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
         <v>15916993174</v>
       </c>
-      <c r="B617" t="n">
-        <v>1</v>
-      </c>
+      <c r="B617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="n">
         <v>15917688377</v>
       </c>
-      <c r="B618" t="n">
-        <v>0</v>
-      </c>
+      <c r="B618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="n">
         <v>15917716861</v>
       </c>
-      <c r="B619" t="n">
-        <v>0</v>
-      </c>
+      <c r="B619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
         <v>15918334008</v>
       </c>
-      <c r="B620" t="n">
-        <v>0</v>
-      </c>
+      <c r="B620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
         <v>15920212045</v>
       </c>
-      <c r="B621" t="n">
-        <v>0</v>
-      </c>
+      <c r="B621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="n">
         <v>15920217866</v>
       </c>
-      <c r="B622" t="n">
-        <v>1</v>
-      </c>
+      <c r="B622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="n">
         <v>15920227724</v>
       </c>
-      <c r="B623" t="n">
-        <v>0</v>
-      </c>
+      <c r="B623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
         <v>15920229250</v>
       </c>
-      <c r="B624" t="n">
-        <v>0</v>
-      </c>
+      <c r="B624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="n">
         <v>15920255722</v>
       </c>
-      <c r="B625" t="n">
-        <v>0</v>
-      </c>
+      <c r="B625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
         <v>15920297684</v>
       </c>
-      <c r="B626" t="n">
-        <v>0</v>
-      </c>
+      <c r="B626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">
         <v>15920692721</v>
       </c>
-      <c r="B627" t="n">
-        <v>0</v>
-      </c>
+      <c r="B627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="n">
         <v>15989657722</v>
       </c>
-      <c r="B628" t="n">
-        <v>1</v>
-      </c>
+      <c r="B628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="n">
         <v>15989915056</v>
       </c>
-      <c r="B629" t="n">
-        <v>0</v>
-      </c>
+      <c r="B629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="n">
         <v>15992750153</v>
       </c>
-      <c r="B630" t="n">
-        <v>1</v>
-      </c>
+      <c r="B630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="n">
         <v>15992807607</v>
       </c>
-      <c r="B631" t="n">
-        <v>1</v>
-      </c>
+      <c r="B631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="n">
         <v>15992812379</v>
       </c>
-      <c r="B632" t="n">
-        <v>1</v>
-      </c>
+      <c r="B632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
         <v>15992912582</v>
       </c>
-      <c r="B633" t="n">
-        <v>1</v>
-      </c>
+      <c r="B633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="n">
         <v>15992943951</v>
       </c>
-      <c r="B634" t="n">
-        <v>0</v>
-      </c>
+      <c r="B634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="n">
         <v>15999714483</v>
       </c>
-      <c r="B635" t="n">
-        <v>1</v>
-      </c>
+      <c r="B635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="n">
         <v>15999757370</v>
       </c>
-      <c r="B636" t="n">
-        <v>0</v>
-      </c>
+      <c r="B636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="n">
         <v>15999801782</v>
       </c>
-      <c r="B637" t="n">
-        <v>1</v>
-      </c>
+      <c r="B637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="n">
         <v>15999835064</v>
       </c>
-      <c r="B638" t="n">
-        <v>0</v>
-      </c>
+      <c r="B638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="n">
         <v>15999866362</v>
       </c>
-      <c r="B639" t="n">
-        <v>0</v>
-      </c>
+      <c r="B639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="n">
         <v>16620600158</v>
       </c>
-      <c r="B640" t="n">
-        <v>0</v>
-      </c>
+      <c r="B640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="n">
         <v>16676560506</v>
       </c>
-      <c r="B641" t="n">
-        <v>1</v>
-      </c>
+      <c r="B641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="n">
         <v>17322108985</v>
       </c>
-      <c r="B642" t="n">
-        <v>1</v>
-      </c>
+      <c r="B642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="n">
         <v>17620575867</v>
       </c>
-      <c r="B643" t="n">
-        <v>1</v>
-      </c>
+      <c r="B643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="n">
         <v>17825055203</v>
       </c>
-      <c r="B644" t="n">
-        <v>0</v>
-      </c>
+      <c r="B644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="n">
         <v>17825057929</v>
       </c>
-      <c r="B645" t="n">
-        <v>0</v>
-      </c>
+      <c r="B645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="n">
         <v>17825065855</v>
       </c>
-      <c r="B646" t="n">
-        <v>0</v>
-      </c>
+      <c r="B646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="n">
         <v>17825512210</v>
       </c>
-      <c r="B647" t="n">
-        <v>0</v>
-      </c>
+      <c r="B647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="n">
         <v>17841381165</v>
       </c>
-      <c r="B648" t="n">
-        <v>1</v>
-      </c>
+      <c r="B648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="n">
         <v>18028202086</v>
       </c>
-      <c r="B649" t="n">
-        <v>1</v>
-      </c>
+      <c r="B649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="n">
         <v>18200640606</v>
       </c>
-      <c r="B650" t="n">
-        <v>0</v>
-      </c>
+      <c r="B650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="n">
         <v>18200647882</v>
       </c>
-      <c r="B651" t="n">
-        <v>0</v>
-      </c>
+      <c r="B651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="n">
         <v>18218034783</v>
       </c>
-      <c r="B652" t="n">
-        <v>1</v>
-      </c>
+      <c r="B652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="n">
         <v>18218289839</v>
       </c>
-      <c r="B653" t="n">
-        <v>1</v>
-      </c>
+      <c r="B653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
         <v>18316599574</v>
       </c>
-      <c r="B654" t="n">
-        <v>0</v>
-      </c>
+      <c r="B654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="n">
         <v>18316778830</v>
       </c>
-      <c r="B655" t="n">
-        <v>0</v>
-      </c>
+      <c r="B655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="n">
         <v>18316831832</v>
       </c>
-      <c r="B656" t="n">
-        <v>1</v>
-      </c>
+      <c r="B656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="n">
         <v>18319192636</v>
       </c>
-      <c r="B657" t="n">
-        <v>0</v>
-      </c>
+      <c r="B657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="n">
         <v>18319198491</v>
       </c>
-      <c r="B658" t="n">
-        <v>0</v>
-      </c>
+      <c r="B658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="n">
         <v>18319681583</v>
       </c>
-      <c r="B659" t="n">
-        <v>0</v>
-      </c>
+      <c r="B659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="n">
         <v>18319845482</v>
       </c>
-      <c r="B660" t="n">
-        <v>1</v>
-      </c>
+      <c r="B660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="n">
         <v>18319871110</v>
       </c>
-      <c r="B661" t="n">
-        <v>1</v>
-      </c>
+      <c r="B661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="n">
         <v>18575360150</v>
       </c>
-      <c r="B662" t="n">
-        <v>1</v>
-      </c>
+      <c r="B662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="n">
         <v>18617227398</v>
       </c>
-      <c r="B663" t="n">
-        <v>1</v>
-      </c>
+      <c r="B663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="n">
         <v>18664041286</v>
       </c>
-      <c r="B664" t="n">
-        <v>1</v>
-      </c>
+      <c r="B664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="n">
         <v>18676281520</v>
       </c>
-      <c r="B665" t="n">
-        <v>1</v>
-      </c>
+      <c r="B665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="n">
         <v>18681196588</v>
       </c>
-      <c r="B666" t="n">
-        <v>1</v>
-      </c>
+      <c r="B666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="n">
         <v>18819095550</v>
       </c>
-      <c r="B667" t="n">
-        <v>1</v>
-      </c>
+      <c r="B667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="n">
         <v>18819515476</v>
       </c>
-      <c r="B668" t="n">
-        <v>1</v>
-      </c>
+      <c r="B668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="n">
         <v>18819529542</v>
       </c>
-      <c r="B669" t="n">
-        <v>1</v>
-      </c>
+      <c r="B669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="n">
         <v>18819529607</v>
       </c>
-      <c r="B670" t="n">
-        <v>1</v>
-      </c>
+      <c r="B670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="n">
         <v>18819716894</v>
       </c>
-      <c r="B671" t="n">
-        <v>1</v>
-      </c>
+      <c r="B671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="n">
         <v>18820613120</v>
       </c>
-      <c r="B672" t="n">
-        <v>1</v>
-      </c>
+      <c r="B672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="n">
         <v>18824215560</v>
       </c>
-      <c r="B673" t="n">
-        <v>0</v>
-      </c>
+      <c r="B673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="n">
         <v>18824218525</v>
       </c>
-      <c r="B674" t="n">
-        <v>0</v>
-      </c>
+      <c r="B674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="n">
         <v>18824524452</v>
       </c>
-      <c r="B675" t="n">
-        <v>0</v>
-      </c>
+      <c r="B675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="n">
         <v>18824547819</v>
       </c>
-      <c r="B676" t="n">
-        <v>1</v>
-      </c>
+      <c r="B676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="n">
         <v>18824578908</v>
       </c>
-      <c r="B677" t="n">
-        <v>0</v>
-      </c>
+      <c r="B677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="n">
         <v>18825506001</v>
       </c>
-      <c r="B678" t="n">
-        <v>0</v>
-      </c>
+      <c r="B678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="n">
         <v>18825506128</v>
       </c>
-      <c r="B679" t="n">
-        <v>0</v>
-      </c>
+      <c r="B679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="n">
         <v>18825562320</v>
       </c>
-      <c r="B680" t="n">
-        <v>0</v>
-      </c>
+      <c r="B680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="n">
         <v>18825566727</v>
       </c>
-      <c r="B681" t="n">
-        <v>1</v>
-      </c>
+      <c r="B681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="n">
         <v>18825755520</v>
       </c>
-      <c r="B682" t="n">
-        <v>0</v>
-      </c>
+      <c r="B682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="n">
         <v>18825763644</v>
       </c>
-      <c r="B683" t="n">
-        <v>0</v>
-      </c>
+      <c r="B683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="n">
         <v>18825786930</v>
       </c>
-      <c r="B684" t="n">
-        <v>0</v>
-      </c>
+      <c r="B684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="n">
         <v>18825803885</v>
       </c>
-      <c r="B685" t="n">
-        <v>0</v>
-      </c>
+      <c r="B685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="n">
         <v>18825827943</v>
       </c>
-      <c r="B686" t="n">
-        <v>1</v>
-      </c>
+      <c r="B686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="n">
         <v>18825828363</v>
       </c>
-      <c r="B687" t="n">
-        <v>1</v>
-      </c>
+      <c r="B687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="n">
         <v>18825837564</v>
       </c>
-      <c r="B688" t="n">
-        <v>0</v>
-      </c>
+      <c r="B688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="n">
         <v>18825842525</v>
       </c>
-      <c r="B689" t="n">
-        <v>0</v>
-      </c>
+      <c r="B689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="n">
         <v>18825864934</v>
       </c>
-      <c r="B690" t="n">
-        <v>0</v>
-      </c>
+      <c r="B690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="n">
         <v>18826801936</v>
       </c>
-      <c r="B691" t="n">
-        <v>0</v>
-      </c>
+      <c r="B691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="n">
         <v>18826810906</v>
       </c>
-      <c r="B692" t="n">
-        <v>0</v>
-      </c>
+      <c r="B692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="n">
         <v>18826812718</v>
       </c>
-      <c r="B693" t="n">
-        <v>0</v>
-      </c>
+      <c r="B693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="n">
         <v>18826855849</v>
       </c>
-      <c r="B694" t="n">
-        <v>1</v>
-      </c>
+      <c r="B694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="n">
         <v>18826898824</v>
       </c>
-      <c r="B695" t="n">
-        <v>0</v>
-      </c>
+      <c r="B695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="n">
         <v>18826963812</v>
       </c>
-      <c r="B696" t="n">
-        <v>1</v>
-      </c>
+      <c r="B696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="n">
         <v>18826989491</v>
       </c>
-      <c r="B697" t="n">
-        <v>0</v>
-      </c>
+      <c r="B697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="n">
         <v>18898711134</v>
       </c>
-      <c r="B698" t="n">
-        <v>1</v>
-      </c>
+      <c r="B698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="n">
         <v>18938585886</v>
       </c>
-      <c r="B699" t="n">
-        <v>1</v>
-      </c>
+      <c r="B699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="n">
         <v>19521709945</v>
       </c>
-      <c r="B700" t="n">
-        <v>0</v>
-      </c>
+      <c r="B700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="n">
         <v>19521801859</v>
       </c>
-      <c r="B701" t="n">
-        <v>0</v>
-      </c>
+      <c r="B701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="n">
         <v>19521822784</v>
       </c>
-      <c r="B702" t="n">
-        <v>1</v>
-      </c>
+      <c r="B702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="n">
         <v>19521848757</v>
       </c>
-      <c r="B703" t="n">
-        <v>0</v>
-      </c>
+      <c r="B703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="n">
         <v>19521892648</v>
       </c>
-      <c r="B704" t="n">
-        <v>0</v>
-      </c>
+      <c r="B704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="n">
         <v>19525634214</v>
       </c>
-      <c r="B705" t="n">
-        <v>0</v>
-      </c>
+      <c r="B705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="n">
         <v>19525699969</v>
       </c>
-      <c r="B706" t="n">
-        <v>0</v>
-      </c>
+      <c r="B706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="n">
         <v>19525997136</v>
       </c>
-      <c r="B707" t="n">
-        <v>0</v>
-      </c>
+      <c r="B707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="n">
         <v>19525999742</v>
       </c>
-      <c r="B708" t="n">
-        <v>0</v>
-      </c>
+      <c r="B708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="n">
         <v>19525999843</v>
       </c>
-      <c r="B709" t="n">
-        <v>0</v>
-      </c>
+      <c r="B709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="n">
         <v>19526618584</v>
       </c>
-      <c r="B710" t="n">
-        <v>1</v>
-      </c>
+      <c r="B710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="n">
         <v>19526622692</v>
       </c>
-      <c r="B711" t="n">
-        <v>0</v>
-      </c>
+      <c r="B711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="n">
         <v>19526644381</v>
       </c>
-      <c r="B712" t="n">
-        <v>0</v>
-      </c>
+      <c r="B712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="n">
         <v>19536818705</v>
       </c>
-      <c r="B713" t="n">
-        <v>0</v>
-      </c>
+      <c r="B713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="n">
         <v>19536827258</v>
       </c>
-      <c r="B714" t="n">
-        <v>0</v>
-      </c>
+      <c r="B714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="n">
         <v>19537654643</v>
       </c>
-      <c r="B715" t="n">
-        <v>0</v>
-      </c>
+      <c r="B715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="n">
         <v>19537906358</v>
       </c>
-      <c r="B716" t="n">
-        <v>0</v>
-      </c>
+      <c r="B716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="n">
         <v>19539422752</v>
       </c>
-      <c r="B717" t="n">
-        <v>0</v>
-      </c>
+      <c r="B717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="n">
         <v>19820120190</v>
       </c>
-      <c r="B718" t="n">
-        <v>0</v>
-      </c>
+      <c r="B718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="n">
         <v>19865592304</v>
       </c>
-      <c r="B719" t="n">
-        <v>0</v>
-      </c>
+      <c r="B719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="n">
         <v>19876938366</v>
       </c>
-      <c r="B720" t="n">
-        <v>0</v>
-      </c>
+      <c r="B720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="n">
         <v>19876969212</v>
       </c>
-      <c r="B721" t="n">
-        <v>1</v>
-      </c>
+      <c r="B721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="n">
         <v>19878970549</v>
       </c>
-      <c r="B722" t="n">
-        <v>0</v>
-      </c>
+      <c r="B722" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/spider_telephone/最终数据.xlsx
+++ b/spider_telephone/最终数据.xlsx
@@ -432,4327 +432,5769 @@
       <c r="A2" t="n">
         <v>13071302896</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>13192099996</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>13215124663</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>13215132859</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>13266012612</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>13266252339</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>13310807198</v>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>13316627678</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>13332627463</v>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>13380159738</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>13380168728</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>13412001694</v>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13412121698</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>13412209436</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>13412209597</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>13412223422</v>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>13412292787</v>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>13412360278</v>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>13412413200</v>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>13412440837</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>13412466407</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>13412474974</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>13412611516</v>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>13412656245</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>13412727974</v>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>13412801160</v>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>13412846148</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>13412882445</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>13412909682</v>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>13412919173</v>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>13412955840</v>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>13414242486</v>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>13415901819</v>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>13415946829</v>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>13415980602</v>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>13415989968</v>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>13416651139</v>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>13416675918</v>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>13416885775</v>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>13416913243</v>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>13416933639</v>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>13416950113</v>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>13416969354</v>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>13418391419</v>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>13418393842</v>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>13421994713</v>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>13423004212</v>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>13423040355</v>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>13423130366</v>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>13423312331</v>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>13423494869</v>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>13424745879</v>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>13428444253</v>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>13428547393</v>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>13431178860</v>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>13431423431</v>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>13431467571</v>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>13431544143</v>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>13433079049</v>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>13433622189</v>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>13433668649</v>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>13434025637</v>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>13434037309</v>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>13434067130</v>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>13434540706</v>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>13434566550</v>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>13437372214</v>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>13437403045</v>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>13437405014</v>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>13437413376</v>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>13437416490</v>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>13437428489</v>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>13450041008</v>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>13450041573</v>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>13450094241</v>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>13450699707</v>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>13480030686</v>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>13480071985</v>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>13480090229</v>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>13480450153</v>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
         <v>13500098229</v>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
         <v>13509022281</v>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
         <v>13509022502</v>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
         <v>13509817757</v>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
         <v>13527916519</v>
       </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
         <v>13527936712</v>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>13527942547</v>
       </c>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
         <v>13527954868</v>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
         <v>13527993664</v>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>13528528636</v>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>13528573727</v>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
         <v>13528605899</v>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
         <v>13528680763</v>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
         <v>13528681975</v>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
         <v>13528697335</v>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
         <v>13532340259</v>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>13532354251</v>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>13532445690</v>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>13532448020</v>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
         <v>13532516038</v>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
         <v>13532524813</v>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>13532535484</v>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
         <v>13532551077</v>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
         <v>13532580390</v>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
         <v>13532637003</v>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>13532671042</v>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
         <v>13532721023</v>
       </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
         <v>13532734521</v>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
         <v>13532739374</v>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
         <v>13532811110</v>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
         <v>13532811552</v>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
         <v>13532823367</v>
       </c>
-      <c r="B113" t="inlineStr"/>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
         <v>13532867526</v>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
         <v>13532880082</v>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
         <v>13532923878</v>
       </c>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
         <v>13532960717</v>
       </c>
-      <c r="B117" t="inlineStr"/>
+      <c r="B117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
         <v>13532987368</v>
       </c>
-      <c r="B118" t="inlineStr"/>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
         <v>13532997658</v>
       </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
         <v>13537043824</v>
       </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
         <v>13537070423</v>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
         <v>13537073529</v>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
         <v>13537076636</v>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
         <v>13537120039</v>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
         <v>13537279956</v>
       </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
         <v>13537283790</v>
       </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
         <v>13537408208</v>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
         <v>13537475612</v>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>13537485150</v>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>13538359694</v>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
         <v>13538429979</v>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
         <v>13538479625</v>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
         <v>13538480693</v>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
         <v>13538493223</v>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
         <v>13538550559</v>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
         <v>13538581083</v>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
         <v>13538634531</v>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
         <v>13538665688</v>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
         <v>13538687965</v>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
         <v>13539002592</v>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
         <v>13539002647</v>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
         <v>13539024025</v>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
         <v>13539038864</v>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
         <v>13539039426</v>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
         <v>13539047897</v>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
         <v>13539062216</v>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>13539086306</v>
       </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
         <v>13539089464</v>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
         <v>13539093337</v>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
         <v>13543743066</v>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
         <v>13543753670</v>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
         <v>13544654843</v>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
         <v>13544676043</v>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
         <v>13544689762</v>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
         <v>13544709181</v>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
         <v>13544710506</v>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
         <v>13544720070</v>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
         <v>13544721794</v>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
         <v>13544766231</v>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
         <v>13544863168</v>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
         <v>13546911933</v>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
         <v>13546946294</v>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
         <v>13546962609</v>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
         <v>13546996722</v>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
         <v>13549213072</v>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
         <v>13549282116</v>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
         <v>13549292803</v>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
         <v>13549376864</v>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
         <v>13553828700</v>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
         <v>13553867048</v>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
         <v>13556604212</v>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
         <v>13556656667</v>
       </c>
-      <c r="B172" t="inlineStr"/>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
         <v>13556685837</v>
       </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
         <v>13556698476</v>
       </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
         <v>13556729591</v>
       </c>
-      <c r="B175" t="inlineStr"/>
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
         <v>13556785927</v>
       </c>
-      <c r="B176" t="inlineStr"/>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
         <v>13559751560</v>
       </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
         <v>13559782669</v>
       </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="B178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
         <v>13559794591</v>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
         <v>13560801360</v>
       </c>
-      <c r="B180" t="inlineStr"/>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
         <v>13560828081</v>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
         <v>13560863234</v>
       </c>
-      <c r="B182" t="inlineStr"/>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
         <v>13560878619</v>
       </c>
-      <c r="B183" t="inlineStr"/>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
         <v>13580753744</v>
       </c>
-      <c r="B184" t="inlineStr"/>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
         <v>13580797529</v>
       </c>
-      <c r="B185" t="inlineStr"/>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
         <v>13580816168</v>
       </c>
-      <c r="B186" t="inlineStr"/>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
         <v>13580828044</v>
       </c>
-      <c r="B187" t="inlineStr"/>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
         <v>13580829686</v>
       </c>
-      <c r="B188" t="inlineStr"/>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
         <v>13580859588</v>
       </c>
-      <c r="B189" t="inlineStr"/>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
         <v>13580868178</v>
       </c>
-      <c r="B190" t="inlineStr"/>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
         <v>13580880920</v>
       </c>
-      <c r="B191" t="inlineStr"/>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
         <v>13580911586</v>
       </c>
-      <c r="B192" t="inlineStr"/>
+      <c r="B192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
         <v>13580956429</v>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
         <v>13580967518</v>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
         <v>13592714548</v>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
         <v>13592751620</v>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
         <v>13592770869</v>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
         <v>13600242465</v>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
         <v>13600256222</v>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
         <v>13600271603</v>
       </c>
-      <c r="B200" t="inlineStr"/>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
         <v>13602333496</v>
       </c>
-      <c r="B201" t="inlineStr"/>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
         <v>13602363442</v>
       </c>
-      <c r="B202" t="inlineStr"/>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
         <v>13602364926</v>
       </c>
-      <c r="B203" t="inlineStr"/>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
         <v>13602368245</v>
       </c>
-      <c r="B204" t="inlineStr"/>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
         <v>13602373651</v>
       </c>
-      <c r="B205" t="inlineStr"/>
+      <c r="B205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
         <v>13602377728</v>
       </c>
-      <c r="B206" t="inlineStr"/>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
         <v>13602382083</v>
       </c>
-      <c r="B207" t="inlineStr"/>
+      <c r="B207" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
         <v>13602396639</v>
       </c>
-      <c r="B208" t="inlineStr"/>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
         <v>13602396803</v>
       </c>
-      <c r="B209" t="inlineStr"/>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
         <v>13609661189</v>
       </c>
-      <c r="B210" t="inlineStr"/>
+      <c r="B210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
         <v>13612699272</v>
       </c>
-      <c r="B211" t="inlineStr"/>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
         <v>13612759585</v>
       </c>
-      <c r="B212" t="inlineStr"/>
+      <c r="B212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
         <v>13620055268</v>
       </c>
-      <c r="B213" t="inlineStr"/>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
         <v>13622680860</v>
       </c>
-      <c r="B214" t="inlineStr"/>
+      <c r="B214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
         <v>13622682273</v>
       </c>
-      <c r="B215" t="inlineStr"/>
+      <c r="B215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
         <v>13622696269</v>
       </c>
-      <c r="B216" t="inlineStr"/>
+      <c r="B216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
         <v>13631793071</v>
       </c>
-      <c r="B217" t="inlineStr"/>
+      <c r="B217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
         <v>13642380866</v>
       </c>
-      <c r="B218" t="inlineStr"/>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
         <v>13642800825</v>
       </c>
-      <c r="B219" t="inlineStr"/>
+      <c r="B219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
         <v>13642820787</v>
       </c>
-      <c r="B220" t="inlineStr"/>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
         <v>13642907152</v>
       </c>
-      <c r="B221" t="inlineStr"/>
+      <c r="B221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
         <v>13642912597</v>
       </c>
-      <c r="B222" t="inlineStr"/>
+      <c r="B222" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
         <v>13642918499</v>
       </c>
-      <c r="B223" t="inlineStr"/>
+      <c r="B223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
         <v>13642952310</v>
       </c>
-      <c r="B224" t="inlineStr"/>
+      <c r="B224" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
         <v>13649802461</v>
       </c>
-      <c r="B225" t="inlineStr"/>
+      <c r="B225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
         <v>13649820818</v>
       </c>
-      <c r="B226" t="inlineStr"/>
+      <c r="B226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
         <v>13650004673</v>
       </c>
-      <c r="B227" t="inlineStr"/>
+      <c r="B227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
         <v>13650011102</v>
       </c>
-      <c r="B228" t="inlineStr"/>
+      <c r="B228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
         <v>13650034071</v>
       </c>
-      <c r="B229" t="inlineStr"/>
+      <c r="B229" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
         <v>13650035066</v>
       </c>
-      <c r="B230" t="inlineStr"/>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
         <v>13650082478</v>
       </c>
-      <c r="B231" t="inlineStr"/>
+      <c r="B231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
         <v>13650094520</v>
       </c>
-      <c r="B232" t="inlineStr"/>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
         <v>13650155157</v>
       </c>
-      <c r="B233" t="inlineStr"/>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
         <v>13650218460</v>
       </c>
-      <c r="B234" t="inlineStr"/>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
         <v>13650241680</v>
       </c>
-      <c r="B235" t="inlineStr"/>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
         <v>13650260987</v>
       </c>
-      <c r="B236" t="inlineStr"/>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
         <v>13650373337</v>
       </c>
-      <c r="B237" t="inlineStr"/>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
         <v>13650381441</v>
       </c>
-      <c r="B238" t="inlineStr"/>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
         <v>13650382662</v>
       </c>
-      <c r="B239" t="inlineStr"/>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
         <v>13650399497</v>
       </c>
-      <c r="B240" t="inlineStr"/>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
         <v>13650429899</v>
       </c>
-      <c r="B241" t="inlineStr"/>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
         <v>13650448911</v>
       </c>
-      <c r="B242" t="inlineStr"/>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
         <v>13652488338</v>
       </c>
-      <c r="B243" t="inlineStr"/>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
         <v>13652490789</v>
       </c>
-      <c r="B244" t="inlineStr"/>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
         <v>13652510966</v>
       </c>
-      <c r="B245" t="inlineStr"/>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
         <v>13652521899</v>
       </c>
-      <c r="B246" t="inlineStr"/>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
         <v>13652525818</v>
       </c>
-      <c r="B247" t="inlineStr"/>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
         <v>13652530798</v>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
         <v>13652537477</v>
       </c>
-      <c r="B249" t="inlineStr"/>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
         <v>13652573083</v>
       </c>
-      <c r="B250" t="inlineStr"/>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
         <v>13662732748</v>
       </c>
-      <c r="B251" t="inlineStr"/>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
         <v>13662773663</v>
       </c>
-      <c r="B252" t="inlineStr"/>
+      <c r="B252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
         <v>13662780007</v>
       </c>
-      <c r="B253" t="inlineStr"/>
+      <c r="B253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
         <v>13662789728</v>
       </c>
-      <c r="B254" t="inlineStr"/>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
         <v>13662801795</v>
       </c>
-      <c r="B255" t="inlineStr"/>
+      <c r="B255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
         <v>13662831504</v>
       </c>
-      <c r="B256" t="inlineStr"/>
+      <c r="B256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
         <v>13662883917</v>
       </c>
-      <c r="B257" t="inlineStr"/>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
         <v>13662892550</v>
       </c>
-      <c r="B258" t="inlineStr"/>
+      <c r="B258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
         <v>13662924782</v>
       </c>
-      <c r="B259" t="inlineStr"/>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
         <v>13662927220</v>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
         <v>13662978731</v>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
         <v>13662999728</v>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
         <v>13669803831</v>
       </c>
-      <c r="B263" t="inlineStr"/>
+      <c r="B263" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
         <v>13669877757</v>
       </c>
-      <c r="B264" t="inlineStr"/>
+      <c r="B264" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
         <v>13669882415</v>
       </c>
-      <c r="B265" t="inlineStr"/>
+      <c r="B265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
         <v>13669888939</v>
       </c>
-      <c r="B266" t="inlineStr"/>
+      <c r="B266" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
         <v>13669888944</v>
       </c>
-      <c r="B267" t="inlineStr"/>
+      <c r="B267" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
         <v>13669895661</v>
       </c>
-      <c r="B268" t="inlineStr"/>
+      <c r="B268" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
         <v>13669899465</v>
       </c>
-      <c r="B269" t="inlineStr"/>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
         <v>13686049100</v>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
         <v>13686053379</v>
       </c>
-      <c r="B271" t="inlineStr"/>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
         <v>13686093776</v>
       </c>
-      <c r="B272" t="inlineStr"/>
+      <c r="B272" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
         <v>13686098107</v>
       </c>
-      <c r="B273" t="inlineStr"/>
+      <c r="B273" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
         <v>13686110392</v>
       </c>
-      <c r="B274" t="inlineStr"/>
+      <c r="B274" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
         <v>13686144095</v>
       </c>
-      <c r="B275" t="inlineStr"/>
+      <c r="B275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
         <v>13686213715</v>
       </c>
-      <c r="B276" t="inlineStr"/>
+      <c r="B276" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
         <v>13686216306</v>
       </c>
-      <c r="B277" t="inlineStr"/>
+      <c r="B277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
         <v>13686601052</v>
       </c>
-      <c r="B278" t="inlineStr"/>
+      <c r="B278" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
         <v>13686601655</v>
       </c>
-      <c r="B279" t="inlineStr"/>
+      <c r="B279" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
         <v>13686695138</v>
       </c>
-      <c r="B280" t="inlineStr"/>
+      <c r="B280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
         <v>13694912028</v>
       </c>
-      <c r="B281" t="inlineStr"/>
+      <c r="B281" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
         <v>13694941815</v>
       </c>
-      <c r="B282" t="inlineStr"/>
+      <c r="B282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
         <v>13694997368</v>
       </c>
-      <c r="B283" t="inlineStr"/>
+      <c r="B283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
         <v>13711812362</v>
       </c>
-      <c r="B284" t="inlineStr"/>
+      <c r="B284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
         <v>13711873141</v>
       </c>
-      <c r="B285" t="inlineStr"/>
+      <c r="B285" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
         <v>13711877045</v>
       </c>
-      <c r="B286" t="inlineStr"/>
+      <c r="B286" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
         <v>13711879718</v>
       </c>
-      <c r="B287" t="inlineStr"/>
+      <c r="B287" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
         <v>13711894720</v>
       </c>
-      <c r="B288" t="inlineStr"/>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
         <v>13711896171</v>
       </c>
-      <c r="B289" t="inlineStr"/>
+      <c r="B289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
         <v>13711930666</v>
       </c>
-      <c r="B290" t="inlineStr"/>
+      <c r="B290" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
         <v>13711936262</v>
       </c>
-      <c r="B291" t="inlineStr"/>
+      <c r="B291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
         <v>13711968145</v>
       </c>
-      <c r="B292" t="inlineStr"/>
+      <c r="B292" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
         <v>13711977757</v>
       </c>
-      <c r="B293" t="inlineStr"/>
+      <c r="B293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
         <v>13711984987</v>
       </c>
-      <c r="B294" t="inlineStr"/>
+      <c r="B294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
         <v>13711991951</v>
       </c>
-      <c r="B295" t="inlineStr"/>
+      <c r="B295" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
         <v>13711993776</v>
       </c>
-      <c r="B296" t="inlineStr"/>
+      <c r="B296" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
         <v>13712019467</v>
       </c>
-      <c r="B297" t="inlineStr"/>
+      <c r="B297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
         <v>13712052155</v>
       </c>
-      <c r="B298" t="inlineStr"/>
+      <c r="B298" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
         <v>13712096023</v>
       </c>
-      <c r="B299" t="inlineStr"/>
+      <c r="B299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
         <v>13712112289</v>
       </c>
-      <c r="B300" t="inlineStr"/>
+      <c r="B300" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
         <v>13712226612</v>
       </c>
-      <c r="B301" t="inlineStr"/>
+      <c r="B301" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
         <v>13712263752</v>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
         <v>13712268749</v>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
         <v>13712280944</v>
       </c>
-      <c r="B304" t="inlineStr"/>
+      <c r="B304" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
         <v>13712291786</v>
       </c>
-      <c r="B305" t="inlineStr"/>
+      <c r="B305" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
         <v>13712299996</v>
       </c>
-      <c r="B306" t="inlineStr"/>
+      <c r="B306" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
         <v>13712320699</v>
       </c>
-      <c r="B307" t="inlineStr"/>
+      <c r="B307" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
         <v>13712344703</v>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
         <v>13712353422</v>
       </c>
-      <c r="B309" t="inlineStr"/>
+      <c r="B309" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
         <v>13712355082</v>
       </c>
-      <c r="B310" t="inlineStr"/>
+      <c r="B310" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
         <v>13712355738</v>
       </c>
-      <c r="B311" t="inlineStr"/>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
         <v>13712389828</v>
       </c>
-      <c r="B312" t="inlineStr"/>
+      <c r="B312" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
         <v>13712449158</v>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
         <v>13712452369</v>
       </c>
-      <c r="B314" t="inlineStr"/>
+      <c r="B314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
         <v>13712516068</v>
       </c>
-      <c r="B315" t="inlineStr"/>
+      <c r="B315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
         <v>13712558108</v>
       </c>
-      <c r="B316" t="inlineStr"/>
+      <c r="B316" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
         <v>13712586603</v>
       </c>
-      <c r="B317" t="inlineStr"/>
+      <c r="B317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
         <v>13712619108</v>
       </c>
-      <c r="B318" t="inlineStr"/>
+      <c r="B318" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
         <v>13712662691</v>
       </c>
-      <c r="B319" t="inlineStr"/>
+      <c r="B319" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
         <v>13712699109</v>
       </c>
-      <c r="B320" t="inlineStr"/>
+      <c r="B320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
         <v>13712723949</v>
       </c>
-      <c r="B321" t="inlineStr"/>
+      <c r="B321" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
         <v>13712733431</v>
       </c>
-      <c r="B322" t="inlineStr"/>
+      <c r="B322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
         <v>13712733600</v>
       </c>
-      <c r="B323" t="inlineStr"/>
+      <c r="B323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
         <v>13712743010</v>
       </c>
-      <c r="B324" t="inlineStr"/>
+      <c r="B324" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
         <v>13712765119</v>
       </c>
-      <c r="B325" t="inlineStr"/>
+      <c r="B325" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
         <v>13712815826</v>
       </c>
-      <c r="B326" t="inlineStr"/>
+      <c r="B326" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
         <v>13712839586</v>
       </c>
-      <c r="B327" t="inlineStr"/>
+      <c r="B327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
         <v>13712855578</v>
       </c>
-      <c r="B328" t="inlineStr"/>
+      <c r="B328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
         <v>13712872847</v>
       </c>
-      <c r="B329" t="inlineStr"/>
+      <c r="B329" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
         <v>13712904380</v>
       </c>
-      <c r="B330" t="inlineStr"/>
+      <c r="B330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
         <v>13712998075</v>
       </c>
-      <c r="B331" t="inlineStr"/>
+      <c r="B331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
         <v>13713003738</v>
       </c>
-      <c r="B332" t="inlineStr"/>
+      <c r="B332" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
         <v>13713074257</v>
       </c>
-      <c r="B333" t="inlineStr"/>
+      <c r="B333" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
         <v>13713086699</v>
       </c>
-      <c r="B334" t="inlineStr"/>
+      <c r="B334" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
         <v>13713115909</v>
       </c>
-      <c r="B335" t="inlineStr"/>
+      <c r="B335" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
         <v>13713136083</v>
       </c>
-      <c r="B336" t="inlineStr"/>
+      <c r="B336" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
         <v>13713198390</v>
       </c>
-      <c r="B337" t="inlineStr"/>
+      <c r="B337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
         <v>13713198711</v>
       </c>
-      <c r="B338" t="inlineStr"/>
+      <c r="B338" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
         <v>13713204685</v>
       </c>
-      <c r="B339" t="inlineStr"/>
+      <c r="B339" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
         <v>13713223897</v>
       </c>
-      <c r="B340" t="inlineStr"/>
+      <c r="B340" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
         <v>13713308329</v>
       </c>
-      <c r="B341" t="inlineStr"/>
+      <c r="B341" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
         <v>13713337846</v>
       </c>
-      <c r="B342" t="inlineStr"/>
+      <c r="B342" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
         <v>13713409077</v>
       </c>
-      <c r="B343" t="inlineStr"/>
+      <c r="B343" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
         <v>13713434111</v>
       </c>
-      <c r="B344" t="inlineStr"/>
+      <c r="B344" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
         <v>13713444007</v>
       </c>
-      <c r="B345" t="inlineStr"/>
+      <c r="B345" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
         <v>13717151972</v>
       </c>
-      <c r="B346" t="inlineStr"/>
+      <c r="B346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
         <v>13717307240</v>
       </c>
-      <c r="B347" t="inlineStr"/>
+      <c r="B347" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
         <v>13717383282</v>
       </c>
-      <c r="B348" t="inlineStr"/>
+      <c r="B348" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
         <v>13723500388</v>
       </c>
-      <c r="B349" t="inlineStr"/>
+      <c r="B349" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
         <v>13723510133</v>
       </c>
-      <c r="B350" t="inlineStr"/>
+      <c r="B350" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
         <v>13723558415</v>
       </c>
-      <c r="B351" t="inlineStr"/>
+      <c r="B351" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
         <v>13723569673</v>
       </c>
-      <c r="B352" t="inlineStr"/>
+      <c r="B352" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
         <v>13723596261</v>
       </c>
-      <c r="B353" t="inlineStr"/>
+      <c r="B353" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
         <v>13724439128</v>
       </c>
-      <c r="B354" t="inlineStr"/>
+      <c r="B354" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
         <v>13724450035</v>
       </c>
-      <c r="B355" t="inlineStr"/>
+      <c r="B355" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
         <v>13724464119</v>
       </c>
-      <c r="B356" t="inlineStr"/>
+      <c r="B356" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
         <v>13724479441</v>
       </c>
-      <c r="B357" t="inlineStr"/>
+      <c r="B357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
         <v>13725707485</v>
       </c>
-      <c r="B358" t="inlineStr"/>
+      <c r="B358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
         <v>13725800358</v>
       </c>
-      <c r="B359" t="inlineStr"/>
+      <c r="B359" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
         <v>13725826806</v>
       </c>
-      <c r="B360" t="inlineStr"/>
+      <c r="B360" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
         <v>13726417549</v>
       </c>
-      <c r="B361" t="inlineStr"/>
+      <c r="B361" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
         <v>13726442133</v>
       </c>
-      <c r="B362" t="inlineStr"/>
+      <c r="B362" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
         <v>13726498649</v>
       </c>
-      <c r="B363" t="inlineStr"/>
+      <c r="B363" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
         <v>13728149426</v>
       </c>
-      <c r="B364" t="inlineStr"/>
+      <c r="B364" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
         <v>13728151231</v>
       </c>
-      <c r="B365" t="inlineStr"/>
+      <c r="B365" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
         <v>13728163275</v>
       </c>
-      <c r="B366" t="inlineStr"/>
+      <c r="B366" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
         <v>13728185013</v>
       </c>
-      <c r="B367" t="inlineStr"/>
+      <c r="B367" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
         <v>13728204165</v>
       </c>
-      <c r="B368" t="inlineStr"/>
+      <c r="B368" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
         <v>13728219490</v>
       </c>
-      <c r="B369" t="inlineStr"/>
+      <c r="B369" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
         <v>13728236582</v>
       </c>
-      <c r="B370" t="inlineStr"/>
+      <c r="B370" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
         <v>13728240079</v>
       </c>
-      <c r="B371" t="inlineStr"/>
+      <c r="B371" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
         <v>13728327228</v>
       </c>
-      <c r="B372" t="inlineStr"/>
+      <c r="B372" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
         <v>13728341239</v>
       </c>
-      <c r="B373" t="inlineStr"/>
+      <c r="B373" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
         <v>13728390010</v>
       </c>
-      <c r="B374" t="inlineStr"/>
+      <c r="B374" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
         <v>13728411491</v>
       </c>
-      <c r="B375" t="inlineStr"/>
+      <c r="B375" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
         <v>13728452399</v>
       </c>
-      <c r="B376" t="inlineStr"/>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
         <v>13728483197</v>
       </c>
-      <c r="B377" t="inlineStr"/>
+      <c r="B377" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
         <v>13729920018</v>
       </c>
-      <c r="B378" t="inlineStr"/>
+      <c r="B378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
         <v>13729921556</v>
       </c>
-      <c r="B379" t="inlineStr"/>
+      <c r="B379" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
         <v>13729956831</v>
       </c>
-      <c r="B380" t="inlineStr"/>
+      <c r="B380" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
         <v>13729983984</v>
       </c>
-      <c r="B381" t="inlineStr"/>
+      <c r="B381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
         <v>13751234067</v>
       </c>
-      <c r="B382" t="inlineStr"/>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
         <v>13751271392</v>
       </c>
-      <c r="B383" t="inlineStr"/>
+      <c r="B383" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
         <v>13751272740</v>
       </c>
-      <c r="B384" t="inlineStr"/>
+      <c r="B384" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
         <v>13751274207</v>
       </c>
-      <c r="B385" t="inlineStr"/>
+      <c r="B385" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
         <v>13751293361</v>
       </c>
-      <c r="B386" t="inlineStr"/>
+      <c r="B386" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
         <v>13751419235</v>
       </c>
-      <c r="B387" t="inlineStr"/>
+      <c r="B387" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
         <v>13763174190</v>
       </c>
-      <c r="B388" t="inlineStr"/>
+      <c r="B388" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
         <v>13763175212</v>
       </c>
-      <c r="B389" t="inlineStr"/>
+      <c r="B389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
         <v>13763193133</v>
       </c>
-      <c r="B390" t="inlineStr"/>
+      <c r="B390" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
         <v>13763220454</v>
       </c>
-      <c r="B391" t="inlineStr"/>
+      <c r="B391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
         <v>13763231696</v>
       </c>
-      <c r="B392" t="inlineStr"/>
+      <c r="B392" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
         <v>13790136902</v>
       </c>
-      <c r="B393" t="inlineStr"/>
+      <c r="B393" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
         <v>13790155991</v>
       </c>
-      <c r="B394" t="inlineStr"/>
+      <c r="B394" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
         <v>13790159430</v>
       </c>
-      <c r="B395" t="inlineStr"/>
+      <c r="B395" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
         <v>13790222165</v>
       </c>
-      <c r="B396" t="inlineStr"/>
+      <c r="B396" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
         <v>13790252808</v>
       </c>
-      <c r="B397" t="inlineStr"/>
+      <c r="B397" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
         <v>13790296326</v>
       </c>
-      <c r="B398" t="inlineStr"/>
+      <c r="B398" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
         <v>13790313316</v>
       </c>
-      <c r="B399" t="inlineStr"/>
+      <c r="B399" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
         <v>13790319372</v>
       </c>
-      <c r="B400" t="inlineStr"/>
+      <c r="B400" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
         <v>13790352650</v>
       </c>
-      <c r="B401" t="inlineStr"/>
+      <c r="B401" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
         <v>13790371035</v>
       </c>
-      <c r="B402" t="inlineStr"/>
+      <c r="B402" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
         <v>13790393954</v>
       </c>
-      <c r="B403" t="inlineStr"/>
+      <c r="B403" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
         <v>13790405589</v>
       </c>
-      <c r="B404" t="inlineStr"/>
+      <c r="B404" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
         <v>13790419056</v>
       </c>
-      <c r="B405" t="inlineStr"/>
+      <c r="B405" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
         <v>13790421095</v>
       </c>
-      <c r="B406" t="inlineStr"/>
+      <c r="B406" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
         <v>13790458353</v>
       </c>
-      <c r="B407" t="inlineStr"/>
+      <c r="B407" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
         <v>13790483302</v>
       </c>
-      <c r="B408" t="inlineStr"/>
+      <c r="B408" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
         <v>13790494488</v>
       </c>
-      <c r="B409" t="inlineStr"/>
+      <c r="B409" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
         <v>13790494902</v>
       </c>
-      <c r="B410" t="inlineStr"/>
+      <c r="B410" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
         <v>13790578973</v>
       </c>
-      <c r="B411" t="inlineStr"/>
+      <c r="B411" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
         <v>13790601572</v>
       </c>
-      <c r="B412" t="inlineStr"/>
+      <c r="B412" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
         <v>13790683138</v>
       </c>
-      <c r="B413" t="inlineStr"/>
+      <c r="B413" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
         <v>13790687776</v>
       </c>
-      <c r="B414" t="inlineStr"/>
+      <c r="B414" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
         <v>13790689947</v>
       </c>
-      <c r="B415" t="inlineStr"/>
+      <c r="B415" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
         <v>13790691705</v>
       </c>
-      <c r="B416" t="inlineStr"/>
+      <c r="B416" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
         <v>13794868255</v>
       </c>
-      <c r="B417" t="inlineStr"/>
+      <c r="B417" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
         <v>13794949764</v>
       </c>
-      <c r="B418" t="inlineStr"/>
+      <c r="B418" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
         <v>13798781472</v>
       </c>
-      <c r="B419" t="inlineStr"/>
+      <c r="B419" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
         <v>13798781690</v>
       </c>
-      <c r="B420" t="inlineStr"/>
+      <c r="B420" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
         <v>13798823821</v>
       </c>
-      <c r="B421" t="inlineStr"/>
+      <c r="B421" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
         <v>13798843237</v>
       </c>
-      <c r="B422" t="inlineStr"/>
+      <c r="B422" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
         <v>13798855625</v>
       </c>
-      <c r="B423" t="inlineStr"/>
+      <c r="B423" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
         <v>13798856719</v>
       </c>
-      <c r="B424" t="inlineStr"/>
+      <c r="B424" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
         <v>13798881331</v>
       </c>
-      <c r="B425" t="inlineStr"/>
+      <c r="B425" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
         <v>13798895886</v>
       </c>
-      <c r="B426" t="inlineStr"/>
+      <c r="B426" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
         <v>13798896320</v>
       </c>
-      <c r="B427" t="inlineStr"/>
+      <c r="B427" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
         <v>13798898561</v>
       </c>
-      <c r="B428" t="inlineStr"/>
+      <c r="B428" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
         <v>13798930665</v>
       </c>
-      <c r="B429" t="inlineStr"/>
+      <c r="B429" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
         <v>13798933533</v>
       </c>
-      <c r="B430" t="inlineStr"/>
+      <c r="B430" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
         <v>13802386445</v>
       </c>
-      <c r="B431" t="inlineStr"/>
+      <c r="B431" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
         <v>13802397109</v>
       </c>
-      <c r="B432" t="inlineStr"/>
+      <c r="B432" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
         <v>13809616372</v>
       </c>
-      <c r="B433" t="inlineStr"/>
+      <c r="B433" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
         <v>13809619132</v>
       </c>
-      <c r="B434" t="inlineStr"/>
+      <c r="B434" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
         <v>13809644011</v>
       </c>
-      <c r="B435" t="inlineStr"/>
+      <c r="B435" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
         <v>13809827203</v>
       </c>
-      <c r="B436" t="inlineStr"/>
+      <c r="B436" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
         <v>13825720922</v>
       </c>
-      <c r="B437" t="inlineStr"/>
+      <c r="B437" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
         <v>13825730587</v>
       </c>
-      <c r="B438" t="inlineStr"/>
+      <c r="B438" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
         <v>13825764627</v>
       </c>
-      <c r="B439" t="inlineStr"/>
+      <c r="B439" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
         <v>13825778943</v>
       </c>
-      <c r="B440" t="inlineStr"/>
+      <c r="B440" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
         <v>13825780799</v>
       </c>
-      <c r="B441" t="inlineStr"/>
+      <c r="B441" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
         <v>13826944862</v>
       </c>
-      <c r="B442" t="inlineStr"/>
+      <c r="B442" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
         <v>13826958639</v>
       </c>
-      <c r="B443" t="inlineStr"/>
+      <c r="B443" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
         <v>13826985060</v>
       </c>
-      <c r="B444" t="inlineStr"/>
+      <c r="B444" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
         <v>13827230263</v>
       </c>
-      <c r="B445" t="inlineStr"/>
+      <c r="B445" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
         <v>13827244150</v>
       </c>
-      <c r="B446" t="inlineStr"/>
+      <c r="B446" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
         <v>13827244258</v>
       </c>
-      <c r="B447" t="inlineStr"/>
+      <c r="B447" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
         <v>13827244347</v>
       </c>
-      <c r="B448" t="inlineStr"/>
+      <c r="B448" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
         <v>13827247099</v>
       </c>
-      <c r="B449" t="inlineStr"/>
+      <c r="B449" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
         <v>13827279440</v>
       </c>
-      <c r="B450" t="inlineStr"/>
+      <c r="B450" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
         <v>13827299884</v>
       </c>
-      <c r="B451" t="inlineStr"/>
+      <c r="B451" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
         <v>13829118773</v>
       </c>
-      <c r="B452" t="inlineStr"/>
+      <c r="B452" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
         <v>13829134489</v>
       </c>
-      <c r="B453" t="inlineStr"/>
+      <c r="B453" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
         <v>13829159456</v>
       </c>
-      <c r="B454" t="inlineStr"/>
+      <c r="B454" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
         <v>13829220547</v>
       </c>
-      <c r="B455" t="inlineStr"/>
+      <c r="B455" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
         <v>13829225427</v>
       </c>
-      <c r="B456" t="inlineStr"/>
+      <c r="B456" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
         <v>13829233780</v>
       </c>
-      <c r="B457" t="inlineStr"/>
+      <c r="B457" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
         <v>13829250308</v>
       </c>
-      <c r="B458" t="inlineStr"/>
+      <c r="B458" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
         <v>13829252724</v>
       </c>
-      <c r="B459" t="inlineStr"/>
+      <c r="B459" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
         <v>13829253711</v>
       </c>
-      <c r="B460" t="inlineStr"/>
+      <c r="B460" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
         <v>13829269116</v>
       </c>
-      <c r="B461" t="inlineStr"/>
+      <c r="B461" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
         <v>13829283209</v>
       </c>
-      <c r="B462" t="inlineStr"/>
+      <c r="B462" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
         <v>13902605162</v>
       </c>
-      <c r="B463" t="inlineStr"/>
+      <c r="B463" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
         <v>13902615601</v>
       </c>
-      <c r="B464" t="inlineStr"/>
+      <c r="B464" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
         <v>13902646515</v>
       </c>
-      <c r="B465" t="inlineStr"/>
+      <c r="B465" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
         <v>13903034038</v>
       </c>
-      <c r="B466" t="inlineStr"/>
+      <c r="B466" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
         <v>13922535233</v>
       </c>
-      <c r="B467" t="inlineStr"/>
+      <c r="B467" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
         <v>13922909248</v>
       </c>
-      <c r="B468" t="inlineStr"/>
+      <c r="B468" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
         <v>13922920808</v>
       </c>
-      <c r="B469" t="inlineStr"/>
+      <c r="B469" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
         <v>13922954099</v>
       </c>
-      <c r="B470" t="inlineStr"/>
+      <c r="B470" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
         <v>13922963288</v>
       </c>
-      <c r="B471" t="inlineStr"/>
+      <c r="B471" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
         <v>13922969663</v>
       </c>
-      <c r="B472" t="inlineStr"/>
+      <c r="B472" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
         <v>13924338129</v>
       </c>
-      <c r="B473" t="inlineStr"/>
+      <c r="B473" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
         <v>13924338938</v>
       </c>
-      <c r="B474" t="inlineStr"/>
+      <c r="B474" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
         <v>13924352371</v>
       </c>
-      <c r="B475" t="inlineStr"/>
+      <c r="B475" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
         <v>13924364713</v>
       </c>
-      <c r="B476" t="inlineStr"/>
+      <c r="B476" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
         <v>13925503695</v>
       </c>
-      <c r="B477" t="inlineStr"/>
+      <c r="B477" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
         <v>13925513168</v>
       </c>
-      <c r="B478" t="inlineStr"/>
+      <c r="B478" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
         <v>13925560363</v>
       </c>
-      <c r="B479" t="inlineStr"/>
+      <c r="B479" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
         <v>13925569861</v>
       </c>
-      <c r="B480" t="inlineStr"/>
+      <c r="B480" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
         <v>13925583326</v>
       </c>
-      <c r="B481" t="inlineStr"/>
+      <c r="B481" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
         <v>13925705688</v>
       </c>
-      <c r="B482" t="inlineStr"/>
+      <c r="B482" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
         <v>13925718972</v>
       </c>
-      <c r="B483" t="inlineStr"/>
+      <c r="B483" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
         <v>13925730397</v>
       </c>
-      <c r="B484" t="inlineStr"/>
+      <c r="B484" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
         <v>13925760616</v>
       </c>
-      <c r="B485" t="inlineStr"/>
+      <c r="B485" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
         <v>13925771228</v>
       </c>
-      <c r="B486" t="inlineStr"/>
+      <c r="B486" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
         <v>13925771790</v>
       </c>
-      <c r="B487" t="inlineStr"/>
+      <c r="B487" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
         <v>13925843386</v>
       </c>
-      <c r="B488" t="inlineStr"/>
+      <c r="B488" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
         <v>13925888518</v>
       </c>
-      <c r="B489" t="inlineStr"/>
+      <c r="B489" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
         <v>13926804679</v>
       </c>
-      <c r="B490" t="inlineStr"/>
+      <c r="B490" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
         <v>13926812360</v>
       </c>
-      <c r="B491" t="inlineStr"/>
+      <c r="B491" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
         <v>13926873805</v>
       </c>
-      <c r="B492" t="inlineStr"/>
+      <c r="B492" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
         <v>13929201550</v>
       </c>
-      <c r="B493" t="inlineStr"/>
+      <c r="B493" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
         <v>13929215076</v>
       </c>
-      <c r="B494" t="inlineStr"/>
+      <c r="B494" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
         <v>13929228563</v>
       </c>
-      <c r="B495" t="inlineStr"/>
+      <c r="B495" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
         <v>13929247995</v>
       </c>
-      <c r="B496" t="inlineStr"/>
+      <c r="B496" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
         <v>13929276298</v>
       </c>
-      <c r="B497" t="inlineStr"/>
+      <c r="B497" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
         <v>13929279018</v>
       </c>
-      <c r="B498" t="inlineStr"/>
+      <c r="B498" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
         <v>13929283191</v>
       </c>
-      <c r="B499" t="inlineStr"/>
+      <c r="B499" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
         <v>13929441962</v>
       </c>
-      <c r="B500" t="inlineStr"/>
+      <c r="B500" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
         <v>13929474685</v>
       </c>
-      <c r="B501" t="inlineStr"/>
+      <c r="B501" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
         <v>14707616466</v>
       </c>
-      <c r="B502" t="inlineStr"/>
+      <c r="B502" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
         <v>14716177455</v>
       </c>
-      <c r="B503" t="inlineStr"/>
+      <c r="B503" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
         <v>14778641467</v>
       </c>
-      <c r="B504" t="inlineStr"/>
+      <c r="B504" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
         <v>15007690545</v>
       </c>
-      <c r="B505" t="inlineStr"/>
+      <c r="B505" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
         <v>15014875182</v>
       </c>
-      <c r="B506" t="inlineStr"/>
+      <c r="B506" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
         <v>15014880970</v>
       </c>
-      <c r="B507" t="inlineStr"/>
+      <c r="B507" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
         <v>15015110519</v>
       </c>
-      <c r="B508" t="inlineStr"/>
+      <c r="B508" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
         <v>15015148634</v>
       </c>
-      <c r="B509" t="inlineStr"/>
+      <c r="B509" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
         <v>15015157762</v>
       </c>
-      <c r="B510" t="inlineStr"/>
+      <c r="B510" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
         <v>15015315631</v>
       </c>
-      <c r="B511" t="inlineStr"/>
+      <c r="B511" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
         <v>15015325567</v>
       </c>
-      <c r="B512" t="inlineStr"/>
+      <c r="B512" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
         <v>15015348580</v>
       </c>
-      <c r="B513" t="inlineStr"/>
+      <c r="B513" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
         <v>15015370313</v>
       </c>
-      <c r="B514" t="inlineStr"/>
+      <c r="B514" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
         <v>15015385461</v>
       </c>
-      <c r="B515" t="inlineStr"/>
+      <c r="B515" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
         <v>15015385723</v>
       </c>
-      <c r="B516" t="inlineStr"/>
+      <c r="B516" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
         <v>15015388412</v>
       </c>
-      <c r="B517" t="inlineStr"/>
+      <c r="B517" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
         <v>15015419780</v>
       </c>
-      <c r="B518" t="inlineStr"/>
+      <c r="B518" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
         <v>15015450642</v>
       </c>
-      <c r="B519" t="inlineStr"/>
+      <c r="B519" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
         <v>15016775470</v>
       </c>
-      <c r="B520" t="inlineStr"/>
+      <c r="B520" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
         <v>15016775542</v>
       </c>
-      <c r="B521" t="inlineStr"/>
+      <c r="B521" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
         <v>15016776574</v>
       </c>
-      <c r="B522" t="inlineStr"/>
+      <c r="B522" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
         <v>15016779196</v>
       </c>
-      <c r="B523" t="inlineStr"/>
+      <c r="B523" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
         <v>15016783174</v>
       </c>
-      <c r="B524" t="inlineStr"/>
+      <c r="B524" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
         <v>15016849818</v>
       </c>
-      <c r="B525" t="inlineStr"/>
+      <c r="B525" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
         <v>15016853982</v>
       </c>
-      <c r="B526" t="inlineStr"/>
+      <c r="B526" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
         <v>15016954375</v>
       </c>
-      <c r="B527" t="inlineStr"/>
+      <c r="B527" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
         <v>15016968735</v>
       </c>
-      <c r="B528" t="inlineStr"/>
+      <c r="B528" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
         <v>15017065662</v>
       </c>
-      <c r="B529" t="inlineStr"/>
+      <c r="B529" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
         <v>15017076023</v>
       </c>
-      <c r="B530" t="inlineStr"/>
+      <c r="B530" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
         <v>15017143265</v>
       </c>
-      <c r="B531" t="inlineStr"/>
+      <c r="B531" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
         <v>15017158272</v>
       </c>
-      <c r="B532" t="inlineStr"/>
+      <c r="B532" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
         <v>15017850411</v>
       </c>
-      <c r="B533" t="inlineStr"/>
+      <c r="B533" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
         <v>15017883106</v>
       </c>
-      <c r="B534" t="inlineStr"/>
+      <c r="B534" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
         <v>15019002825</v>
       </c>
-      <c r="B535" t="inlineStr"/>
+      <c r="B535" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
         <v>15019004181</v>
       </c>
-      <c r="B536" t="inlineStr"/>
+      <c r="B536" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
         <v>15019119782</v>
       </c>
-      <c r="B537" t="inlineStr"/>
+      <c r="B537" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
         <v>15019168048</v>
       </c>
-      <c r="B538" t="inlineStr"/>
+      <c r="B538" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
         <v>15019961972</v>
       </c>
-      <c r="B539" t="inlineStr"/>
+      <c r="B539" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
         <v>15019963656</v>
       </c>
-      <c r="B540" t="inlineStr"/>
+      <c r="B540" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
         <v>15019983945</v>
       </c>
-      <c r="B541" t="inlineStr"/>
+      <c r="B541" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
         <v>15019987392</v>
       </c>
-      <c r="B542" t="inlineStr"/>
+      <c r="B542" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
         <v>15019989607</v>
       </c>
-      <c r="B543" t="inlineStr"/>
+      <c r="B543" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
         <v>15024022860</v>
       </c>
-      <c r="B544" t="inlineStr"/>
+      <c r="B544" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
         <v>15024169015</v>
       </c>
-      <c r="B545" t="inlineStr"/>
+      <c r="B545" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
         <v>15099714814</v>
       </c>
-      <c r="B546" t="inlineStr"/>
+      <c r="B546" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
         <v>15099722917</v>
       </c>
-      <c r="B547" t="inlineStr"/>
+      <c r="B547" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
         <v>15112786347</v>
       </c>
-      <c r="B548" t="inlineStr"/>
+      <c r="B548" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
         <v>15112788834</v>
       </c>
-      <c r="B549" t="inlineStr"/>
+      <c r="B549" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
         <v>15118204578</v>
       </c>
-      <c r="B550" t="inlineStr"/>
+      <c r="B550" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
         <v>15118255586</v>
       </c>
-      <c r="B551" t="inlineStr"/>
+      <c r="B551" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
         <v>15118280737</v>
       </c>
-      <c r="B552" t="inlineStr"/>
+      <c r="B552" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
         <v>15118438320</v>
       </c>
-      <c r="B553" t="inlineStr"/>
+      <c r="B553" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
         <v>15118462270</v>
       </c>
-      <c r="B554" t="inlineStr"/>
+      <c r="B554" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
         <v>15118533191</v>
       </c>
-      <c r="B555" t="inlineStr"/>
+      <c r="B555" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
         <v>15118551905</v>
       </c>
-      <c r="B556" t="inlineStr"/>
+      <c r="B556" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
         <v>15217106101</v>
       </c>
-      <c r="B557" t="inlineStr"/>
+      <c r="B557" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
         <v>15217236545</v>
       </c>
-      <c r="B558" t="inlineStr"/>
+      <c r="B558" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
         <v>15217251148</v>
       </c>
-      <c r="B559" t="inlineStr"/>
+      <c r="B559" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
         <v>15217256381</v>
       </c>
-      <c r="B560" t="inlineStr"/>
+      <c r="B560" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
         <v>15217536847</v>
       </c>
-      <c r="B561" t="inlineStr"/>
+      <c r="B561" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
         <v>15218752704</v>
       </c>
-      <c r="B562" t="inlineStr"/>
+      <c r="B562" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
         <v>15220296709</v>
       </c>
-      <c r="B563" t="inlineStr"/>
+      <c r="B563" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
         <v>15220326653</v>
       </c>
-      <c r="B564" t="inlineStr"/>
+      <c r="B564" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
         <v>15220332826</v>
       </c>
-      <c r="B565" t="inlineStr"/>
+      <c r="B565" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
         <v>15220335349</v>
       </c>
-      <c r="B566" t="inlineStr"/>
+      <c r="B566" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
         <v>15220384233</v>
       </c>
-      <c r="B567" t="inlineStr"/>
+      <c r="B567" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
         <v>15724016772</v>
       </c>
-      <c r="B568" t="inlineStr"/>
+      <c r="B568" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
         <v>15728120848</v>
       </c>
-      <c r="B569" t="inlineStr"/>
+      <c r="B569" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
         <v>15728133005</v>
       </c>
-      <c r="B570" t="inlineStr"/>
+      <c r="B570" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
         <v>15728138776</v>
       </c>
-      <c r="B571" t="inlineStr"/>
+      <c r="B571" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
         <v>15790452120</v>
       </c>
-      <c r="B572" t="inlineStr"/>
+      <c r="B572" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
         <v>15807692329</v>
       </c>
-      <c r="B573" t="inlineStr"/>
+      <c r="B573" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
         <v>15812810568</v>
       </c>
-      <c r="B574" t="inlineStr"/>
+      <c r="B574" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
         <v>15814224987</v>
       </c>
-      <c r="B575" t="inlineStr"/>
+      <c r="B575" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
         <v>15814231903</v>
       </c>
-      <c r="B576" t="inlineStr"/>
+      <c r="B576" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
         <v>15814292949</v>
       </c>
-      <c r="B577" t="inlineStr"/>
+      <c r="B577" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
         <v>15816811227</v>
       </c>
-      <c r="B578" t="inlineStr"/>
+      <c r="B578" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
         <v>15816827822</v>
       </c>
-      <c r="B579" t="inlineStr"/>
+      <c r="B579" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
         <v>15816838490</v>
       </c>
-      <c r="B580" t="inlineStr"/>
+      <c r="B580" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
         <v>15817534868</v>
       </c>
-      <c r="B581" t="inlineStr"/>
+      <c r="B581" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
         <v>15817549270</v>
       </c>
-      <c r="B582" t="inlineStr"/>
+      <c r="B582" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
         <v>15817674097</v>
       </c>
-      <c r="B583" t="inlineStr"/>
+      <c r="B583" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
         <v>15817703818</v>
       </c>
-      <c r="B584" t="inlineStr"/>
+      <c r="B584" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
         <v>15817710814</v>
       </c>
-      <c r="B585" t="inlineStr"/>
+      <c r="B585" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
         <v>15817731091</v>
       </c>
-      <c r="B586" t="inlineStr"/>
+      <c r="B586" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
         <v>15817748048</v>
       </c>
-      <c r="B587" t="inlineStr"/>
+      <c r="B587" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
         <v>15817753386</v>
       </c>
-      <c r="B588" t="inlineStr"/>
+      <c r="B588" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
         <v>15817772392</v>
       </c>
-      <c r="B589" t="inlineStr"/>
+      <c r="B589" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
         <v>15817778626</v>
       </c>
-      <c r="B590" t="inlineStr"/>
+      <c r="B590" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
         <v>15818243519</v>
       </c>
-      <c r="B591" t="inlineStr"/>
+      <c r="B591" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
         <v>15818266917</v>
       </c>
-      <c r="B592" t="inlineStr"/>
+      <c r="B592" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
         <v>15818314036</v>
       </c>
-      <c r="B593" t="inlineStr"/>
+      <c r="B593" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
         <v>15818321755</v>
       </c>
-      <c r="B594" t="inlineStr"/>
+      <c r="B594" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
         <v>15818351451</v>
       </c>
-      <c r="B595" t="inlineStr"/>
+      <c r="B595" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
         <v>15818383218</v>
       </c>
-      <c r="B596" t="inlineStr"/>
+      <c r="B596" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
         <v>15818395126</v>
       </c>
-      <c r="B597" t="inlineStr"/>
+      <c r="B597" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
         <v>15818449151</v>
       </c>
-      <c r="B598" t="inlineStr"/>
+      <c r="B598" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
         <v>15818449949</v>
       </c>
-      <c r="B599" t="inlineStr"/>
+      <c r="B599" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
         <v>15820852256</v>
       </c>
-      <c r="B600" t="inlineStr"/>
+      <c r="B600" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
         <v>15820886548</v>
       </c>
-      <c r="B601" t="inlineStr"/>
+      <c r="B601" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
         <v>15876417711</v>
       </c>
-      <c r="B602" t="inlineStr"/>
+      <c r="B602" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
         <v>15899692258</v>
       </c>
-      <c r="B603" t="inlineStr"/>
+      <c r="B603" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
         <v>15899939920</v>
       </c>
-      <c r="B604" t="inlineStr"/>
+      <c r="B604" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
         <v>15913720570</v>
       </c>
-      <c r="B605" t="inlineStr"/>
+      <c r="B605" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
         <v>15913834502</v>
       </c>
-      <c r="B606" t="inlineStr"/>
+      <c r="B606" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
         <v>15916713329</v>
       </c>
-      <c r="B607" t="inlineStr"/>
+      <c r="B607" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
         <v>15916750954</v>
       </c>
-      <c r="B608" t="inlineStr"/>
+      <c r="B608" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
         <v>15916752520</v>
       </c>
-      <c r="B609" t="inlineStr"/>
+      <c r="B609" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
         <v>15916772379</v>
       </c>
-      <c r="B610" t="inlineStr"/>
+      <c r="B610" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
         <v>15916780621</v>
       </c>
-      <c r="B611" t="inlineStr"/>
+      <c r="B611" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
         <v>15916834038</v>
       </c>
-      <c r="B612" t="inlineStr"/>
+      <c r="B612" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
         <v>15916848357</v>
       </c>
-      <c r="B613" t="inlineStr"/>
+      <c r="B613" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
         <v>15916873383</v>
       </c>
-      <c r="B614" t="inlineStr"/>
+      <c r="B614" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
         <v>15916891272</v>
       </c>
-      <c r="B615" t="inlineStr"/>
+      <c r="B615" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
         <v>15916941618</v>
       </c>
-      <c r="B616" t="inlineStr"/>
+      <c r="B616" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
         <v>15916993174</v>
       </c>
-      <c r="B617" t="inlineStr"/>
+      <c r="B617" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
         <v>15917688377</v>
       </c>
-      <c r="B618" t="inlineStr"/>
+      <c r="B618" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
         <v>15917716861</v>
       </c>
-      <c r="B619" t="inlineStr"/>
+      <c r="B619" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
         <v>15918334008</v>
       </c>
-      <c r="B620" t="inlineStr"/>
+      <c r="B620" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
         <v>15920212045</v>
       </c>
-      <c r="B621" t="inlineStr"/>
+      <c r="B621" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
         <v>15920217866</v>
       </c>
-      <c r="B622" t="inlineStr"/>
+      <c r="B622" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
         <v>15920227724</v>
       </c>
-      <c r="B623" t="inlineStr"/>
+      <c r="B623" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
         <v>15920229250</v>
       </c>
-      <c r="B624" t="inlineStr"/>
+      <c r="B624" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
         <v>15920255722</v>
       </c>
-      <c r="B625" t="inlineStr"/>
+      <c r="B625" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
         <v>15920297684</v>
       </c>
-      <c r="B626" t="inlineStr"/>
+      <c r="B626" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
         <v>15920692721</v>
       </c>
-      <c r="B627" t="inlineStr"/>
+      <c r="B627" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
         <v>15989657722</v>
       </c>
-      <c r="B628" t="inlineStr"/>
+      <c r="B628" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
         <v>15989915056</v>
       </c>
-      <c r="B629" t="inlineStr"/>
+      <c r="B629" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
         <v>15992750153</v>
       </c>
-      <c r="B630" t="inlineStr"/>
+      <c r="B630" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
         <v>15992807607</v>
       </c>
-      <c r="B631" t="inlineStr"/>
+      <c r="B631" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
         <v>15992812379</v>
       </c>
-      <c r="B632" t="inlineStr"/>
+      <c r="B632" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
         <v>15992912582</v>
       </c>
-      <c r="B633" t="inlineStr"/>
+      <c r="B633" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
         <v>15992943951</v>
       </c>
-      <c r="B634" t="inlineStr"/>
+      <c r="B634" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
         <v>15999714483</v>
       </c>
-      <c r="B635" t="inlineStr"/>
+      <c r="B635" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
         <v>15999757370</v>
       </c>
-      <c r="B636" t="inlineStr"/>
+      <c r="B636" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
         <v>15999801782</v>
       </c>
-      <c r="B637" t="inlineStr"/>
+      <c r="B637" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
         <v>15999835064</v>
       </c>
-      <c r="B638" t="inlineStr"/>
+      <c r="B638" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
         <v>15999866362</v>
       </c>
-      <c r="B639" t="inlineStr"/>
+      <c r="B639" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
         <v>16620600158</v>
       </c>
-      <c r="B640" t="inlineStr"/>
+      <c r="B640" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
         <v>16676560506</v>
       </c>
-      <c r="B641" t="inlineStr"/>
+      <c r="B641" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
         <v>17322108985</v>
       </c>
-      <c r="B642" t="inlineStr"/>
+      <c r="B642" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
         <v>17620575867</v>
       </c>
-      <c r="B643" t="inlineStr"/>
+      <c r="B643" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
         <v>17825055203</v>
       </c>
-      <c r="B644" t="inlineStr"/>
+      <c r="B644" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
         <v>17825057929</v>
       </c>
-      <c r="B645" t="inlineStr"/>
+      <c r="B645" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
         <v>17825065855</v>
       </c>
-      <c r="B646" t="inlineStr"/>
+      <c r="B646" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
         <v>17825512210</v>
       </c>
-      <c r="B647" t="inlineStr"/>
+      <c r="B647" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
         <v>17841381165</v>
       </c>
-      <c r="B648" t="inlineStr"/>
+      <c r="B648" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
         <v>18028202086</v>
       </c>
-      <c r="B649" t="inlineStr"/>
+      <c r="B649" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
         <v>18200640606</v>
       </c>
-      <c r="B650" t="inlineStr"/>
+      <c r="B650" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
         <v>18200647882</v>
       </c>
-      <c r="B651" t="inlineStr"/>
+      <c r="B651" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
         <v>18218034783</v>
       </c>
-      <c r="B652" t="inlineStr"/>
+      <c r="B652" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
         <v>18218289839</v>
       </c>
-      <c r="B653" t="inlineStr"/>
+      <c r="B653" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
         <v>18316599574</v>
       </c>
-      <c r="B654" t="inlineStr"/>
+      <c r="B654" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
         <v>18316778830</v>
       </c>
-      <c r="B655" t="inlineStr"/>
+      <c r="B655" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
         <v>18316831832</v>
       </c>
-      <c r="B656" t="inlineStr"/>
+      <c r="B656" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
         <v>18319192636</v>
       </c>
-      <c r="B657" t="inlineStr"/>
+      <c r="B657" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
         <v>18319198491</v>
       </c>
-      <c r="B658" t="inlineStr"/>
+      <c r="B658" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
         <v>18319681583</v>
       </c>
-      <c r="B659" t="inlineStr"/>
+      <c r="B659" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
         <v>18319845482</v>
       </c>
-      <c r="B660" t="inlineStr"/>
+      <c r="B660" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
         <v>18319871110</v>
       </c>
-      <c r="B661" t="inlineStr"/>
+      <c r="B661" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
         <v>18575360150</v>
       </c>
-      <c r="B662" t="inlineStr"/>
+      <c r="B662" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
         <v>18617227398</v>
       </c>
-      <c r="B663" t="inlineStr"/>
+      <c r="B663" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
         <v>18664041286</v>
       </c>
-      <c r="B664" t="inlineStr"/>
+      <c r="B664" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
         <v>18676281520</v>
       </c>
-      <c r="B665" t="inlineStr"/>
+      <c r="B665" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
         <v>18681196588</v>
       </c>
-      <c r="B666" t="inlineStr"/>
+      <c r="B666" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
         <v>18819095550</v>
       </c>
-      <c r="B667" t="inlineStr"/>
+      <c r="B667" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
         <v>18819515476</v>
       </c>
-      <c r="B668" t="inlineStr"/>
+      <c r="B668" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
         <v>18819529542</v>
       </c>
-      <c r="B669" t="inlineStr"/>
+      <c r="B669" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
         <v>18819529607</v>
       </c>
-      <c r="B670" t="inlineStr"/>
+      <c r="B670" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
         <v>18819716894</v>
       </c>
-      <c r="B671" t="inlineStr"/>
+      <c r="B671" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
         <v>18820613120</v>
       </c>
-      <c r="B672" t="inlineStr"/>
+      <c r="B672" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
         <v>18824215560</v>
       </c>
-      <c r="B673" t="inlineStr"/>
+      <c r="B673" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
         <v>18824218525</v>
       </c>
-      <c r="B674" t="inlineStr"/>
+      <c r="B674" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
         <v>18824524452</v>
       </c>
-      <c r="B675" t="inlineStr"/>
+      <c r="B675" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
         <v>18824547819</v>
       </c>
-      <c r="B676" t="inlineStr"/>
+      <c r="B676" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
         <v>18824578908</v>
       </c>
-      <c r="B677" t="inlineStr"/>
+      <c r="B677" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
         <v>18825506001</v>
       </c>
-      <c r="B678" t="inlineStr"/>
+      <c r="B678" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
         <v>18825506128</v>
       </c>
-      <c r="B679" t="inlineStr"/>
+      <c r="B679" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
         <v>18825562320</v>
       </c>
-      <c r="B680" t="inlineStr"/>
+      <c r="B680" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
         <v>18825566727</v>
       </c>
-      <c r="B681" t="inlineStr"/>
+      <c r="B681" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
         <v>18825755520</v>
       </c>
-      <c r="B682" t="inlineStr"/>
+      <c r="B682" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
         <v>18825763644</v>
       </c>
-      <c r="B683" t="inlineStr"/>
+      <c r="B683" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
         <v>18825786930</v>
       </c>
-      <c r="B684" t="inlineStr"/>
+      <c r="B684" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
         <v>18825803885</v>
       </c>
-      <c r="B685" t="inlineStr"/>
+      <c r="B685" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
         <v>18825827943</v>
       </c>
-      <c r="B686" t="inlineStr"/>
+      <c r="B686" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
         <v>18825828363</v>
       </c>
-      <c r="B687" t="inlineStr"/>
+      <c r="B687" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
         <v>18825837564</v>
       </c>
-      <c r="B688" t="inlineStr"/>
+      <c r="B688" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
         <v>18825842525</v>
       </c>
-      <c r="B689" t="inlineStr"/>
+      <c r="B689" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
         <v>18825864934</v>
       </c>
-      <c r="B690" t="inlineStr"/>
+      <c r="B690" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
         <v>18826801936</v>
       </c>
-      <c r="B691" t="inlineStr"/>
+      <c r="B691" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
         <v>18826810906</v>
       </c>
-      <c r="B692" t="inlineStr"/>
+      <c r="B692" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
         <v>18826812718</v>
       </c>
-      <c r="B693" t="inlineStr"/>
+      <c r="B693" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
         <v>18826855849</v>
       </c>
-      <c r="B694" t="inlineStr"/>
+      <c r="B694" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
         <v>18826898824</v>
       </c>
-      <c r="B695" t="inlineStr"/>
+      <c r="B695" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
         <v>18826963812</v>
       </c>
-      <c r="B696" t="inlineStr"/>
+      <c r="B696" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
         <v>18826989491</v>
       </c>
-      <c r="B697" t="inlineStr"/>
+      <c r="B697" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
         <v>18898711134</v>
       </c>
-      <c r="B698" t="inlineStr"/>
+      <c r="B698" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
         <v>18938585886</v>
       </c>
-      <c r="B699" t="inlineStr"/>
+      <c r="B699" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
         <v>19521709945</v>
       </c>
-      <c r="B700" t="inlineStr"/>
+      <c r="B700" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
         <v>19521801859</v>
       </c>
-      <c r="B701" t="inlineStr"/>
+      <c r="B701" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
         <v>19521822784</v>
       </c>
-      <c r="B702" t="inlineStr"/>
+      <c r="B702" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
         <v>19521848757</v>
       </c>
-      <c r="B703" t="inlineStr"/>
+      <c r="B703" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
         <v>19521892648</v>
       </c>
-      <c r="B704" t="inlineStr"/>
+      <c r="B704" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
         <v>19525634214</v>
       </c>
-      <c r="B705" t="inlineStr"/>
+      <c r="B705" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
         <v>19525699969</v>
       </c>
-      <c r="B706" t="inlineStr"/>
+      <c r="B706" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
         <v>19525997136</v>
       </c>
-      <c r="B707" t="inlineStr"/>
+      <c r="B707" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
         <v>19525999742</v>
       </c>
-      <c r="B708" t="inlineStr"/>
+      <c r="B708" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
         <v>19525999843</v>
       </c>
-      <c r="B709" t="inlineStr"/>
+      <c r="B709" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
         <v>19526618584</v>
       </c>
-      <c r="B710" t="inlineStr"/>
+      <c r="B710" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
         <v>19526622692</v>
       </c>
-      <c r="B711" t="inlineStr"/>
+      <c r="B711" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
         <v>19526644381</v>
       </c>
-      <c r="B712" t="inlineStr"/>
+      <c r="B712" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
         <v>19536818705</v>
       </c>
-      <c r="B713" t="inlineStr"/>
+      <c r="B713" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
         <v>19536827258</v>
       </c>
-      <c r="B714" t="inlineStr"/>
+      <c r="B714" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
         <v>19537654643</v>
       </c>
-      <c r="B715" t="inlineStr"/>
+      <c r="B715" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
         <v>19537906358</v>
       </c>
-      <c r="B716" t="inlineStr"/>
+      <c r="B716" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
         <v>19539422752</v>
       </c>
-      <c r="B717" t="inlineStr"/>
+      <c r="B717" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
         <v>19820120190</v>
       </c>
-      <c r="B718" t="inlineStr"/>
+      <c r="B718" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
         <v>19865592304</v>
       </c>
-      <c r="B719" t="inlineStr"/>
+      <c r="B719" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
         <v>19876938366</v>
       </c>
-      <c r="B720" t="inlineStr"/>
+      <c r="B720" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
         <v>19876969212</v>
       </c>
-      <c r="B721" t="inlineStr"/>
+      <c r="B721" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
         <v>19878970549</v>
       </c>
-      <c r="B722" t="inlineStr"/>
+      <c r="B722" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
